--- a/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Order_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Order_by_Sample_Type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t xml:space="preserve">Sample_Type</t>
   </si>
@@ -393,24 +393,24 @@
     <t xml:space="preserve">RBG-16-55-12_Unclassified</t>
   </si>
   <si>
+    <t xml:space="preserve">Isosphaerales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steroidobacterales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD2896-B216_Unclassified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polyangiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR202_clade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rickettsiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Isosphaerales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steroidobacterales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MD2896-B216_Unclassified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polyangiales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAR202_clade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Syntrophobacterales</t>
   </si>
   <si>
@@ -618,9 +618,6 @@
     <t xml:space="preserve">LD1-PB3</t>
   </si>
   <si>
-    <t xml:space="preserve">Chloroplast</t>
-  </si>
-  <si>
     <t xml:space="preserve">VHS-B4-70</t>
   </si>
   <si>
@@ -873,12 +870,12 @@
     <t xml:space="preserve">Dissulfuribacterales</t>
   </si>
   <si>
+    <t xml:space="preserve">Vampirovibrionales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Candidatus_Moranbacteria</t>
   </si>
   <si>
-    <t xml:space="preserve">Vampirovibrionales</t>
-  </si>
-  <si>
     <t xml:space="preserve">DG-56_Unclassified</t>
   </si>
   <si>
@@ -891,13 +888,13 @@
     <t xml:space="preserve">Pedosphaerales</t>
   </si>
   <si>
+    <t xml:space="preserve">Caedibacterales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peptococcales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legionellales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caedibacterales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peptococcales</t>
   </si>
   <si>
     <t xml:space="preserve">Acidobacteriota_Unclassified</t>
@@ -1302,10 +1299,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>16.7646858244718</v>
+        <v>16.7660155360335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.602969756615553</v>
+        <v>0.603036004998651</v>
       </c>
     </row>
     <row r="3">
@@ -1316,10 +1313,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>6.95039909968721</v>
+        <v>6.94977921423593</v>
       </c>
       <c r="D3" t="n">
-        <v>0.207187484471134</v>
+        <v>0.207164846308943</v>
       </c>
     </row>
     <row r="4">
@@ -1330,10 +1327,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.58632514697018</v>
+        <v>4.58631644613354</v>
       </c>
       <c r="D4" t="n">
-        <v>0.265096385530426</v>
+        <v>0.265091787475345</v>
       </c>
     </row>
     <row r="5">
@@ -1344,10 +1341,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>3.96489566136487</v>
+        <v>3.96522201435841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0964690180953352</v>
+        <v>0.0964813776637118</v>
       </c>
     </row>
     <row r="6">
@@ -1358,10 +1355,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>3.90237721076908</v>
+        <v>3.90236928352092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.294835609283535</v>
+        <v>0.294845388288193</v>
       </c>
     </row>
     <row r="7">
@@ -1372,10 +1369,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.83209864387196</v>
+        <v>3.832472214343</v>
       </c>
       <c r="D7" t="n">
-        <v>0.481309325768963</v>
+        <v>0.481365791643633</v>
       </c>
     </row>
     <row r="8">
@@ -1386,10 +1383,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7243080649101</v>
+        <v>3.72399152550915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.053899320325139</v>
+        <v>0.0538939796108262</v>
       </c>
     </row>
     <row r="9">
@@ -1400,10 +1397,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.57005604109655</v>
+        <v>3.56992927019193</v>
       </c>
       <c r="D9" t="n">
-        <v>0.067678707841062</v>
+        <v>0.0676763673466402</v>
       </c>
     </row>
     <row r="10">
@@ -1414,10 +1411,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.21105032549323</v>
+        <v>3.21110959330595</v>
       </c>
       <c r="D10" t="n">
-        <v>0.429298584230496</v>
+        <v>0.429309077052021</v>
       </c>
     </row>
     <row r="11">
@@ -1428,10 +1425,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.16232078616599</v>
+        <v>3.16215100855375</v>
       </c>
       <c r="D11" t="n">
-        <v>0.116745303969716</v>
+        <v>0.116737232641053</v>
       </c>
     </row>
     <row r="12">
@@ -1442,10 +1439,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.90693837065784</v>
+        <v>2.9078237697701</v>
       </c>
       <c r="D12" t="n">
-        <v>0.848514761712234</v>
+        <v>0.848774383302174</v>
       </c>
     </row>
     <row r="13">
@@ -1456,10 +1453,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5676286119938</v>
+        <v>2.56741861006658</v>
       </c>
       <c r="D13" t="n">
-        <v>0.173003772687275</v>
+        <v>0.172986339292606</v>
       </c>
     </row>
     <row r="14">
@@ -1470,10 +1467,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>2.12613898120463</v>
+        <v>2.12638450642753</v>
       </c>
       <c r="D14" t="n">
-        <v>0.185261537986637</v>
+        <v>0.185285944581216</v>
       </c>
     </row>
     <row r="15">
@@ -1484,10 +1481,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.75106759017128</v>
+        <v>1.75138898300309</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1667718000852</v>
+        <v>0.166801682503198</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1495,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.67242531745873</v>
+        <v>1.67246521608243</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0311369296704741</v>
+        <v>0.0311389020714201</v>
       </c>
     </row>
     <row r="17">
@@ -1512,10 +1509,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.55734061781472</v>
+        <v>1.55728726615353</v>
       </c>
       <c r="D17" t="n">
-        <v>0.522080141675004</v>
+        <v>0.522067960073351</v>
       </c>
     </row>
     <row r="18">
@@ -1526,10 +1523,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.48377840736855</v>
+        <v>1.48385256396774</v>
       </c>
       <c r="D18" t="n">
-        <v>0.122826069081501</v>
+        <v>0.122840981953677</v>
       </c>
     </row>
     <row r="19">
@@ -1540,10 +1537,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.23047170899452</v>
+        <v>1.230360372418</v>
       </c>
       <c r="D19" t="n">
-        <v>0.151613823845976</v>
+        <v>0.151602610044505</v>
       </c>
     </row>
     <row r="20">
@@ -1554,10 +1551,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1616757331315</v>
+        <v>1.16178318287229</v>
       </c>
       <c r="D20" t="n">
-        <v>0.176434462685899</v>
+        <v>0.176455029969349</v>
       </c>
     </row>
     <row r="21">
@@ -1568,10 +1565,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.09927252956774</v>
+        <v>1.09924966449056</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0561969872727239</v>
+        <v>0.0561972472643328</v>
       </c>
     </row>
     <row r="22">
@@ -1582,10 +1579,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>1.07883725768623</v>
+        <v>1.07909438235509</v>
       </c>
       <c r="D22" t="n">
-        <v>0.151248824376989</v>
+        <v>0.151281809503949</v>
       </c>
     </row>
     <row r="23">
@@ -1596,10 +1593,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>1.04099497543045</v>
+        <v>1.04107978710251</v>
       </c>
       <c r="D23" t="n">
-        <v>0.142585484141673</v>
+        <v>0.142596189245476</v>
       </c>
     </row>
     <row r="24">
@@ -1610,10 +1607,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>1.03809720764431</v>
+        <v>1.03802377419815</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0873994607559586</v>
+        <v>0.0873912906443307</v>
       </c>
     </row>
     <row r="25">
@@ -1624,10 +1621,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.968131272611667</v>
+        <v>0.96806432673786</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0185739043304981</v>
+        <v>0.0185721689859961</v>
       </c>
     </row>
     <row r="26">
@@ -1638,10 +1635,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.877725207683841</v>
+        <v>0.877831115757872</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0294629724088283</v>
+        <v>0.0294679365530855</v>
       </c>
     </row>
     <row r="27">
@@ -1652,10 +1649,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.857836275493774</v>
+        <v>0.857814410525154</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0857934487131631</v>
+        <v>0.0857903118571765</v>
       </c>
     </row>
     <row r="28">
@@ -1666,10 +1663,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.848467110325538</v>
+        <v>0.84830527092907</v>
       </c>
       <c r="D28" t="n">
-        <v>0.289379225813157</v>
+        <v>0.289314746281158</v>
       </c>
     </row>
     <row r="29">
@@ -1680,10 +1677,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.847008211450436</v>
+        <v>0.846995849931033</v>
       </c>
       <c r="D29" t="n">
-        <v>0.113306239357737</v>
+        <v>0.113302671291891</v>
       </c>
     </row>
     <row r="30">
@@ -1694,10 +1691,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.81557648929784</v>
+        <v>0.815692933747752</v>
       </c>
       <c r="D30" t="n">
-        <v>0.186442344963325</v>
+        <v>0.186476028071674</v>
       </c>
     </row>
     <row r="31">
@@ -1708,10 +1705,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.813202490124236</v>
+        <v>0.813358417192032</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0723325120152498</v>
+        <v>0.0723456617887789</v>
       </c>
     </row>
     <row r="32">
@@ -1722,10 +1719,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.808472130103592</v>
+        <v>0.80850725443698</v>
       </c>
       <c r="D32" t="n">
-        <v>0.154569455135979</v>
+        <v>0.154585340843082</v>
       </c>
     </row>
     <row r="33">
@@ -1736,10 +1733,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.801532046510136</v>
+        <v>0.801452308053329</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0856361291516478</v>
+        <v>0.0856291312265669</v>
       </c>
     </row>
     <row r="34">
@@ -1750,10 +1747,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.801372255229656</v>
+        <v>0.801445435236589</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0431735946637523</v>
+        <v>0.0431733126622106</v>
       </c>
     </row>
     <row r="35">
@@ -1764,10 +1761,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.773990248012892</v>
+        <v>0.773979493112025</v>
       </c>
       <c r="D35" t="n">
-        <v>0.214351784510008</v>
+        <v>0.214333657206</v>
       </c>
     </row>
     <row r="36">
@@ -1778,10 +1775,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.745095754293287</v>
+        <v>0.745126362573919</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0231663501894589</v>
+        <v>0.0231683694809714</v>
       </c>
     </row>
     <row r="37">
@@ -1792,10 +1789,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.720096565413408</v>
+        <v>0.720201420325395</v>
       </c>
       <c r="D37" t="n">
-        <v>0.206764880265126</v>
+        <v>0.20679605167245</v>
       </c>
     </row>
     <row r="38">
@@ -1806,10 +1803,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.717789083657777</v>
+        <v>0.717720333482241</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0904521077802339</v>
+        <v>0.0904446384621796</v>
       </c>
     </row>
     <row r="39">
@@ -1820,10 +1817,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.686982027324757</v>
+        <v>0.687059129209796</v>
       </c>
       <c r="D39" t="n">
-        <v>0.206836216698603</v>
+        <v>0.206854379814775</v>
       </c>
     </row>
     <row r="40">
@@ -1834,10 +1831,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.600174928402651</v>
+        <v>0.600268975302979</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0454330124927653</v>
+        <v>0.0454422721066344</v>
       </c>
     </row>
     <row r="41">
@@ -1848,10 +1845,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.546939917718448</v>
+        <v>0.5469106672692</v>
       </c>
       <c r="D41" t="n">
-        <v>0.236708808884444</v>
+        <v>0.23669411707758</v>
       </c>
     </row>
     <row r="42">
@@ -1862,10 +1859,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.498882054835389</v>
+        <v>0.498942888695507</v>
       </c>
       <c r="D42" t="n">
-        <v>0.020488869352362</v>
+        <v>0.0204910721943635</v>
       </c>
     </row>
     <row r="43">
@@ -1876,10 +1873,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.430293030354796</v>
+        <v>0.430362935082194</v>
       </c>
       <c r="D43" t="n">
-        <v>0.106578730709796</v>
+        <v>0.106595560404305</v>
       </c>
     </row>
     <row r="44">
@@ -1890,10 +1887,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.419048522431741</v>
+        <v>0.419020322211645</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0232657073408555</v>
+        <v>0.0232625777419894</v>
       </c>
     </row>
     <row r="45">
@@ -1904,10 +1901,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.371101721215097</v>
+        <v>0.371162135183143</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0279351985264715</v>
+        <v>0.0279376369729004</v>
       </c>
     </row>
     <row r="46">
@@ -1918,10 +1915,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.370981541430713</v>
+        <v>0.371006525647605</v>
       </c>
       <c r="D46" t="n">
-        <v>0.261471016128176</v>
+        <v>0.261487804319947</v>
       </c>
     </row>
     <row r="47">
@@ -1932,10 +1929,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.346401561761411</v>
+        <v>0.346406996330817</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00848242083577107</v>
+        <v>0.00848308271124754</v>
       </c>
     </row>
     <row r="48">
@@ -1946,10 +1943,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.336323276074375</v>
+        <v>0.336320017196861</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0303813994566529</v>
+        <v>0.0303835110090498</v>
       </c>
     </row>
     <row r="49">
@@ -1960,10 +1957,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.326915919444809</v>
+        <v>0.326897833673444</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0380863898137862</v>
+        <v>0.038084802128229</v>
       </c>
     </row>
     <row r="50">
@@ -1974,10 +1971,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.319671499979457</v>
+        <v>0.319721417724366</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0354458968289284</v>
+        <v>0.0354499598365413</v>
       </c>
     </row>
     <row r="51">
@@ -1988,10 +1985,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.310150166875274</v>
+        <v>0.310114714012385</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0685769544517772</v>
+        <v>0.0685672363066828</v>
       </c>
     </row>
     <row r="52">
@@ -2002,10 +1999,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.287326695472501</v>
+        <v>0.287312426273117</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00994830551201207</v>
+        <v>0.00994771942648803</v>
       </c>
     </row>
     <row r="53">
@@ -2016,10 +2013,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.285782519772783</v>
+        <v>0.28580302124885</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0110716233748312</v>
+        <v>0.0110726452393806</v>
       </c>
     </row>
     <row r="54">
@@ -2030,10 +2027,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.265397098585415</v>
+        <v>0.265415034503111</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0266376021124212</v>
+        <v>0.0266384595257284</v>
       </c>
     </row>
     <row r="55">
@@ -2044,10 +2041,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.26451323905176</v>
+        <v>0.264553691274712</v>
       </c>
       <c r="D55" t="n">
-        <v>0.174994995320914</v>
+        <v>0.175026143200136</v>
       </c>
     </row>
     <row r="56">
@@ -2058,10 +2055,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.242674225434993</v>
+        <v>0.242650323142323</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0224444037160852</v>
+        <v>0.0224418613647339</v>
       </c>
     </row>
     <row r="57">
@@ -2072,10 +2069,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.236699541266215</v>
+        <v>0.236760991536877</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0402695573397131</v>
+        <v>0.0402803860148671</v>
       </c>
     </row>
     <row r="58">
@@ -2086,10 +2083,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.235791615880213</v>
+        <v>0.235759726724195</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0947939764946072</v>
+        <v>0.0947801490926459</v>
       </c>
     </row>
     <row r="59">
@@ -2100,10 +2097,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.226671778921371</v>
+        <v>0.226639648319221</v>
       </c>
       <c r="D59" t="n">
-        <v>0.030802944107052</v>
+        <v>0.0307982994618997</v>
       </c>
     </row>
     <row r="60">
@@ -2114,10 +2111,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.217412479600799</v>
+        <v>0.217459208654182</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0357391999950631</v>
+        <v>0.0357468425513277</v>
       </c>
     </row>
     <row r="61">
@@ -2128,10 +2125,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.214486460596688</v>
+        <v>0.214470579235682</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0387518958895776</v>
+        <v>0.0387484901861466</v>
       </c>
     </row>
     <row r="62">
@@ -2142,10 +2139,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.213394528600517</v>
+        <v>0.213419785319753</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0615196028841004</v>
+        <v>0.0615402836652481</v>
       </c>
     </row>
     <row r="63">
@@ -2156,10 +2153,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.212472477605531</v>
+        <v>0.212479778221493</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00778749582098166</v>
+        <v>0.00778755489389038</v>
       </c>
     </row>
     <row r="64">
@@ -2170,10 +2167,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.208307067205629</v>
+        <v>0.208287658828188</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00817749263951723</v>
+        <v>0.00817667343951784</v>
       </c>
     </row>
     <row r="65">
@@ -2184,10 +2181,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.187426502317055</v>
+        <v>0.187464518196462</v>
       </c>
       <c r="D65" t="n">
-        <v>0.073250465942819</v>
+        <v>0.0732703739551784</v>
       </c>
     </row>
     <row r="66">
@@ -2198,10 +2195,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.184825372319607</v>
+        <v>0.18480018114175</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0604408082587919</v>
+        <v>0.0604306433345011</v>
       </c>
     </row>
     <row r="67">
@@ -2212,10 +2209,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.182669834283909</v>
+        <v>0.182662735135597</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0274990566320673</v>
+        <v>0.0275001011227362</v>
       </c>
     </row>
     <row r="68">
@@ -2226,10 +2223,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.173846261420399</v>
+        <v>0.173839084304802</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0223772991483214</v>
+        <v>0.0223779630723094</v>
       </c>
     </row>
     <row r="69">
@@ -2240,10 +2237,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.173184301003556</v>
+        <v>0.173179144488699</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00969574270892927</v>
+        <v>0.00969541101419215</v>
       </c>
     </row>
     <row r="70">
@@ -2254,10 +2251,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.166865744205456</v>
+        <v>0.166907848622472</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0361995650751186</v>
+        <v>0.0362095481812533</v>
       </c>
     </row>
     <row r="71">
@@ -2268,10 +2265,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.165463796198327</v>
+        <v>0.165473521650637</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0306342297622402</v>
+        <v>0.0306375886581487</v>
       </c>
     </row>
     <row r="72">
@@ -2282,10 +2279,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.147335707117758</v>
+        <v>0.147354684997057</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00663058562165589</v>
+        <v>0.00663086730515384</v>
       </c>
     </row>
     <row r="73">
@@ -2296,10 +2293,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.13028445282164</v>
+        <v>0.130277976533951</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0132887801066265</v>
+        <v>0.0132870685725215</v>
       </c>
     </row>
     <row r="74">
@@ -2310,10 +2307,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.130002389073964</v>
+        <v>0.129988347071982</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0690577404654442</v>
+        <v>0.0690523451853767</v>
       </c>
     </row>
     <row r="75">
@@ -2324,10 +2321,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.127079583832743</v>
+        <v>0.127064486480804</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0268389736915483</v>
+        <v>0.026835761224723</v>
       </c>
     </row>
     <row r="76">
@@ -2338,10 +2335,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.12238225830507</v>
+        <v>0.122391942256463</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00616208044349337</v>
+        <v>0.00616300233622297</v>
       </c>
     </row>
     <row r="77">
@@ -2352,10 +2349,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.114909437458452</v>
+        <v>0.114891980988895</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0178909320574738</v>
+        <v>0.0178852675083426</v>
       </c>
     </row>
     <row r="78">
@@ -2366,10 +2363,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.109250748394383</v>
+        <v>0.109268448100416</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0156842513821768</v>
+        <v>0.0156864711753446</v>
       </c>
     </row>
     <row r="79">
@@ -2380,10 +2377,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.108650223165825</v>
+        <v>0.108685752768108</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0445648033651906</v>
+        <v>0.0445789922726585</v>
       </c>
     </row>
     <row r="80">
@@ -2394,7 +2391,7 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0989603543565518</v>
+        <v>0.0989321799505745</v>
       </c>
       <c r="D80"/>
     </row>
@@ -2406,10 +2403,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0931332790647367</v>
+        <v>0.0931309996902721</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0327415527241503</v>
+        <v>0.0327398335275147</v>
       </c>
     </row>
     <row r="82">
@@ -2420,10 +2417,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0904120440215771</v>
+        <v>0.0904003250131124</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00899418206847615</v>
+        <v>0.00899305994560171</v>
       </c>
     </row>
     <row r="83">
@@ -2434,10 +2431,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.089371158538301</v>
+        <v>0.0893694025021064</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0140737389388145</v>
+        <v>0.0140739801229829</v>
       </c>
     </row>
     <row r="84">
@@ -2448,10 +2445,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0832350388382611</v>
+        <v>0.0832561067163704</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0363058298904643</v>
+        <v>0.0363109553690869</v>
       </c>
     </row>
     <row r="85">
@@ -2462,7 +2459,7 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0828081315444811</v>
+        <v>0.082792415700007</v>
       </c>
       <c r="D85"/>
     </row>
@@ -2474,10 +2471,10 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0818164988459741</v>
+        <v>0.0818285031522164</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00880091303293347</v>
+        <v>0.00880207428062545</v>
       </c>
     </row>
     <row r="87">
@@ -2488,10 +2485,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0805180638993986</v>
+        <v>0.0805411199904651</v>
       </c>
       <c r="D87" t="n">
-        <v>0.04371194544975</v>
+        <v>0.0437238081124717</v>
       </c>
     </row>
     <row r="88">
@@ -2502,10 +2499,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0774329262628541</v>
+        <v>0.0774453642762558</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00543996167827075</v>
+        <v>0.00544061141138761</v>
       </c>
     </row>
     <row r="89">
@@ -2516,10 +2513,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0764141634264545</v>
+        <v>0.0764262450809555</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0121957190481895</v>
+        <v>0.0122015534315381</v>
       </c>
     </row>
     <row r="90">
@@ -2530,10 +2527,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.07513007830488</v>
+        <v>0.0751270586034985</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00978986799512828</v>
+        <v>0.00978935660872495</v>
       </c>
     </row>
     <row r="91">
@@ -2544,10 +2541,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0729235684949596</v>
+        <v>0.0729180456578138</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0032057257921014</v>
+        <v>0.00320533064404325</v>
       </c>
     </row>
     <row r="92">
@@ -2558,10 +2555,10 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0721924000679552</v>
+        <v>0.0721973710589968</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00961270181519435</v>
+        <v>0.00961333231477118</v>
       </c>
     </row>
     <row r="93">
@@ -2572,7 +2569,7 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0674175705375421</v>
+        <v>0.0674220334016752</v>
       </c>
       <c r="D93"/>
     </row>
@@ -2584,10 +2581,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0653591927752883</v>
+        <v>0.0653783415804004</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0335690452409189</v>
+        <v>0.0335781223058521</v>
       </c>
     </row>
     <row r="95">
@@ -2598,10 +2595,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0642012665318477</v>
+        <v>0.0642205707778228</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0298104897478063</v>
+        <v>0.0298195983033222</v>
       </c>
     </row>
     <row r="96">
@@ -2612,10 +2609,10 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0609541701933387</v>
+        <v>0.0609646485517585</v>
       </c>
       <c r="D96" t="n">
-        <v>0.008541867070667</v>
+        <v>0.00854409169289816</v>
       </c>
     </row>
     <row r="97">
@@ -2626,10 +2623,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0597653768784115</v>
+        <v>0.059774455983255</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00368020830547326</v>
+        <v>0.00368083984263925</v>
       </c>
     </row>
     <row r="98">
@@ -2640,10 +2637,10 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0555176044620979</v>
+        <v>0.0555219006253551</v>
       </c>
       <c r="D98" t="n">
-        <v>0.010882824261015</v>
+        <v>0.0108834020325943</v>
       </c>
     </row>
     <row r="99">
@@ -2654,10 +2651,10 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0530687171392698</v>
+        <v>0.0530674085948034</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00649743587405406</v>
+        <v>0.00649680300087323</v>
       </c>
     </row>
     <row r="100">
@@ -2668,10 +2665,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0523916595107067</v>
+        <v>0.0524011935981982</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0156981592493646</v>
+        <v>0.0156982894030075</v>
       </c>
     </row>
     <row r="101">
@@ -2682,10 +2679,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0519347072708309</v>
+        <v>0.0519324973783394</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0252417264053257</v>
+        <v>0.0252417015799962</v>
       </c>
     </row>
     <row r="102">
@@ -2696,10 +2693,10 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0514546607813441</v>
+        <v>0.0514738862700013</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0250685090429189</v>
+        <v>0.025078253122091</v>
       </c>
     </row>
     <row r="103">
@@ -2710,10 +2707,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0510835085367868</v>
+        <v>0.0510840033290636</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00409622825963514</v>
+        <v>0.00409602160930587</v>
       </c>
     </row>
     <row r="104">
@@ -2724,10 +2721,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0507625059410612</v>
+        <v>0.0507547804663097</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0202319309435654</v>
+        <v>0.0202304156172904</v>
       </c>
     </row>
     <row r="105">
@@ -2738,10 +2735,10 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0449328147957303</v>
+        <v>0.0449367916868061</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0096550308536577</v>
+        <v>0.00965379543733032</v>
       </c>
     </row>
     <row r="106">
@@ -2752,10 +2749,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0439272059655816</v>
+        <v>0.0439311193068667</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00281672021647584</v>
+        <v>0.00281725961473784</v>
       </c>
     </row>
     <row r="107">
@@ -2766,7 +2763,7 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0425454373998597</v>
+        <v>0.0425428850299084</v>
       </c>
       <c r="D107"/>
     </row>
@@ -2778,10 +2775,10 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0422022374185856</v>
+        <v>0.042212466894678</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00704739422470973</v>
+        <v>0.00704998638812337</v>
       </c>
     </row>
     <row r="109">
@@ -2792,10 +2789,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0401099282992982</v>
+        <v>0.0401154360391381</v>
       </c>
       <c r="D109" t="n">
-        <v>0.00899770989979867</v>
+        <v>0.00899976873991183</v>
       </c>
     </row>
     <row r="110">
@@ -2806,10 +2803,10 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0399729323137417</v>
+        <v>0.039965354638804</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0223933769823801</v>
+        <v>0.0223895389603966</v>
       </c>
     </row>
     <row r="111">
@@ -2820,10 +2817,10 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0397407192602098</v>
+        <v>0.0397402698905676</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00804735726344126</v>
+        <v>0.00804510732230997</v>
       </c>
     </row>
     <row r="112">
@@ -2834,7 +2831,7 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0390031233074237</v>
+        <v>0.0389926269564989</v>
       </c>
       <c r="D112"/>
     </row>
@@ -2846,10 +2843,10 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0382581282261214</v>
+        <v>0.0382585055423209</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00436572971046813</v>
+        <v>0.00436508619190322</v>
       </c>
     </row>
     <row r="114">
@@ -2860,10 +2857,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0345293411473442</v>
+        <v>0.0345266407570089</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00520283223202059</v>
+        <v>0.00520217535474315</v>
       </c>
     </row>
     <row r="115">
@@ -2874,10 +2871,10 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0337243309125221</v>
+        <v>0.0337274516973899</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00953051381176882</v>
+        <v>0.00953170483544995</v>
       </c>
     </row>
     <row r="116">
@@ -2888,7 +2885,7 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0320950278655328</v>
+        <v>0.032099042357179</v>
       </c>
       <c r="D116"/>
     </row>
@@ -2900,10 +2897,10 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0309265634693571</v>
+        <v>0.0309256583078767</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0107342532055497</v>
+        <v>0.0107352872478775</v>
       </c>
     </row>
     <row r="118">
@@ -2914,10 +2911,10 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.029074987612196</v>
+        <v>0.0290714171741318</v>
       </c>
       <c r="D118" t="n">
-        <v>0.00673156812733868</v>
+        <v>0.00672960975019451</v>
       </c>
     </row>
     <row r="119">
@@ -2928,10 +2925,10 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0287709506949871</v>
+        <v>0.0287743919637144</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00231104155951991</v>
+        <v>0.00231142178275447</v>
       </c>
     </row>
     <row r="120">
@@ -2942,10 +2939,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0272516629730056</v>
+        <v>0.0272525112829742</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00737324011000825</v>
+        <v>0.00737284971391795</v>
       </c>
     </row>
     <row r="121">
@@ -2956,10 +2953,10 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0267603309440648</v>
+        <v>0.026756398500685</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00757188181277581</v>
+        <v>0.00757185639321886</v>
       </c>
     </row>
     <row r="122">
@@ -2970,10 +2967,10 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0265305095280331</v>
+        <v>0.0265273544123701</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00902388670407662</v>
+        <v>0.00902092654466737</v>
       </c>
     </row>
     <row r="123">
@@ -2984,10 +2981,10 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0261796114635553</v>
+        <v>0.025864575824135</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0039546633832143</v>
+        <v>0.00607619540356762</v>
       </c>
     </row>
     <row r="124">
@@ -2998,11 +2995,9 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0258583846518141</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0.00607215497727683</v>
-      </c>
+        <v>0.0257685805033638</v>
+      </c>
+      <c r="D124"/>
     </row>
     <row r="125">
       <c r="A125" t="s">
@@ -3012,9 +3007,11 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0257657086986826</v>
-      </c>
-      <c r="D125"/>
+        <v>0.0256851355435961</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0171872123055681</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
@@ -3024,10 +3021,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0256911195041461</v>
+        <v>0.0249391361091826</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0171909980378978</v>
+        <v>0.00498073052038586</v>
       </c>
     </row>
     <row r="127">
@@ -3038,10 +3035,10 @@
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0249326714619054</v>
+        <v>0.0249247928394642</v>
       </c>
       <c r="D127" t="n">
-        <v>0.00497961849788988</v>
+        <v>0.00762527145775024</v>
       </c>
     </row>
     <row r="128">
@@ -3052,10 +3049,10 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0249274397548737</v>
+        <v>0.0248610698755593</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00762565759969757</v>
+        <v>0.00428015032457145</v>
       </c>
     </row>
     <row r="129">
@@ -3066,10 +3063,10 @@
         <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02468760335681</v>
+        <v>0.0246914905929518</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0039508930761767</v>
+        <v>0.00395200937404464</v>
       </c>
     </row>
     <row r="130">
@@ -3080,10 +3077,10 @@
         <v>133</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0240757178501265</v>
+        <v>0.0240772699490756</v>
       </c>
       <c r="D130" t="n">
-        <v>0.00316824594110922</v>
+        <v>0.00316770989894922</v>
       </c>
     </row>
     <row r="131">
@@ -3094,10 +3091,10 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0239722795282442</v>
+        <v>0.0239732812436176</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00920089725353647</v>
+        <v>0.00920174544280144</v>
       </c>
     </row>
     <row r="132">
@@ -3108,10 +3105,10 @@
         <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0237037434801785</v>
+        <v>0.0237031496639221</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00682263226104706</v>
+        <v>0.00682189265494413</v>
       </c>
     </row>
     <row r="133">
@@ -3122,10 +3119,10 @@
         <v>136</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0235497818161052</v>
+        <v>0.0235532176726475</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0137404847946613</v>
+        <v>0.0137442444457289</v>
       </c>
     </row>
     <row r="134">
@@ -3136,10 +3133,10 @@
         <v>137</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0228190618211321</v>
+        <v>0.0228203662354759</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0126746574829885</v>
+        <v>0.0126752510151411</v>
       </c>
     </row>
     <row r="135">
@@ -3150,10 +3147,10 @@
         <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0222829613277351</v>
+        <v>0.0222802524851444</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00249317401432221</v>
+        <v>0.0024928912067423</v>
       </c>
     </row>
     <row r="136">
@@ -3164,10 +3161,10 @@
         <v>139</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0220213012374824</v>
+        <v>0.0220279005835373</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0143380396374616</v>
+        <v>0.0143421073785844</v>
       </c>
     </row>
     <row r="137">
@@ -3178,10 +3175,10 @@
         <v>140</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0219029899198959</v>
+        <v>0.0219035922459783</v>
       </c>
       <c r="D137" t="n">
-        <v>0.00308503511636453</v>
+        <v>0.00308526430285486</v>
       </c>
     </row>
     <row r="138">
@@ -3192,10 +3189,10 @@
         <v>141</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0218878927081761</v>
+        <v>0.0218882778173728</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00761643845979447</v>
+        <v>0.00761521628056651</v>
       </c>
     </row>
     <row r="139">
@@ -3206,10 +3203,10 @@
         <v>142</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0200565710310945</v>
+        <v>0.020054281611199</v>
       </c>
       <c r="D139" t="n">
-        <v>0.00367870256286118</v>
+        <v>0.00367732895311549</v>
       </c>
     </row>
     <row r="140">
@@ -3220,10 +3217,10 @@
         <v>143</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0189050723134356</v>
+        <v>0.0189074176699697</v>
       </c>
       <c r="D140" t="n">
-        <v>0.00270797388873265</v>
+        <v>0.00270831467486109</v>
       </c>
     </row>
     <row r="141">
@@ -3234,10 +3231,10 @@
         <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0186048470684927</v>
+        <v>0.0186099442323736</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0018945422312154</v>
+        <v>0.0018949136475978</v>
       </c>
     </row>
     <row r="142">
@@ -3248,10 +3245,10 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0184961023009069</v>
+        <v>0.0184993815282947</v>
       </c>
       <c r="D142" t="n">
-        <v>0.00420787379813563</v>
+        <v>0.00420866350133679</v>
       </c>
     </row>
     <row r="143">
@@ -3262,10 +3259,10 @@
         <v>146</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0168851102285283</v>
+        <v>0.0168841948898555</v>
       </c>
       <c r="D143" t="n">
-        <v>0.00254558857207131</v>
+        <v>0.00254521825813036</v>
       </c>
     </row>
     <row r="144">
@@ -3276,10 +3273,10 @@
         <v>147</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0157673933905593</v>
+        <v>0.0157702009417307</v>
       </c>
       <c r="D144" t="n">
-        <v>0.00245065829684617</v>
+        <v>0.00245215881628535</v>
       </c>
     </row>
     <row r="145">
@@ -3290,10 +3287,10 @@
         <v>148</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0157560331124335</v>
+        <v>0.0157595928985015</v>
       </c>
       <c r="D145" t="n">
-        <v>0.00657345294535655</v>
+        <v>0.00657522941771174</v>
       </c>
     </row>
     <row r="146">
@@ -3304,10 +3301,10 @@
         <v>149</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0154686629190539</v>
+        <v>0.0154707104818305</v>
       </c>
       <c r="D146" t="n">
-        <v>0.00784412598664076</v>
+        <v>0.00784546787272763</v>
       </c>
     </row>
     <row r="147">
@@ -3318,10 +3315,10 @@
         <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>0.015449903512412</v>
+        <v>0.0154465809187106</v>
       </c>
       <c r="D147" t="n">
-        <v>0.00589527197923556</v>
+        <v>0.0058945862179202</v>
       </c>
     </row>
     <row r="148">
@@ -3332,7 +3329,7 @@
         <v>151</v>
       </c>
       <c r="C148" t="n">
-        <v>0.014775237521349</v>
+        <v>0.0147781247862119</v>
       </c>
       <c r="D148"/>
     </row>
@@ -3344,7 +3341,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0145945194127426</v>
+        <v>0.0145894211439799</v>
       </c>
       <c r="D149"/>
     </row>
@@ -3356,7 +3353,7 @@
         <v>153</v>
       </c>
       <c r="C150" t="n">
-        <v>0.013743619633386</v>
+        <v>0.0137455587755506</v>
       </c>
       <c r="D150"/>
     </row>
@@ -3368,10 +3365,10 @@
         <v>154</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0129425705481736</v>
+        <v>0.0129449503298657</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00646402454120751</v>
+        <v>0.00646693512033142</v>
       </c>
     </row>
     <row r="152">
@@ -3382,10 +3379,10 @@
         <v>155</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0123602815555546</v>
+        <v>0.0123619561794388</v>
       </c>
       <c r="D152" t="n">
-        <v>0.00145803830815113</v>
+        <v>0.00145885135654017</v>
       </c>
     </row>
     <row r="153">
@@ -3396,7 +3393,7 @@
         <v>156</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0115894268937818</v>
+        <v>0.0115854025923441</v>
       </c>
       <c r="D153"/>
     </row>
@@ -3408,10 +3405,10 @@
         <v>157</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0107167034222362</v>
+        <v>0.010720473546516</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00717874389152424</v>
+        <v>0.00718106385237547</v>
       </c>
     </row>
     <row r="155">
@@ -3422,10 +3419,10 @@
         <v>158</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0105078088343309</v>
+        <v>0.0105113755676532</v>
       </c>
       <c r="D155" t="n">
-        <v>0.000695693990503509</v>
+        <v>0.000696749609857311</v>
       </c>
     </row>
     <row r="156">
@@ -3436,7 +3433,7 @@
         <v>159</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0104810523897978</v>
+        <v>0.0104799249606146</v>
       </c>
       <c r="D156"/>
     </row>
@@ -3448,10 +3445,10 @@
         <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0104315006503412</v>
+        <v>0.0104298729256599</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0047009021687388</v>
+        <v>0.00469981118564176</v>
       </c>
     </row>
     <row r="158">
@@ -3462,10 +3459,10 @@
         <v>161</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0102809022265025</v>
+        <v>0.0102788203664386</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00662758978737952</v>
+        <v>0.00662641101662855</v>
       </c>
     </row>
     <row r="159">
@@ -3476,7 +3473,7 @@
         <v>162</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0102209618116545</v>
+        <v>0.0102228666736311</v>
       </c>
       <c r="D159"/>
     </row>
@@ -3488,10 +3485,10 @@
         <v>163</v>
       </c>
       <c r="C160" t="n">
-        <v>0.00992454823897749</v>
+        <v>0.00992875493987524</v>
       </c>
       <c r="D160" t="n">
-        <v>0.0032327870057732</v>
+        <v>0.0032341818871991</v>
       </c>
     </row>
     <row r="161">
@@ -3502,10 +3499,10 @@
         <v>164</v>
       </c>
       <c r="C161" t="n">
-        <v>0.00915331988384526</v>
+        <v>0.00915548835209094</v>
       </c>
       <c r="D161" t="n">
-        <v>0.00602443303307866</v>
+        <v>0.0060261710001912</v>
       </c>
     </row>
     <row r="162">
@@ -3516,10 +3513,10 @@
         <v>165</v>
       </c>
       <c r="C162" t="n">
-        <v>0.00897476919672336</v>
+        <v>0.00897208873147356</v>
       </c>
       <c r="D162" t="n">
-        <v>0.00287638690041302</v>
+        <v>0.00287464825346117</v>
       </c>
     </row>
     <row r="163">
@@ -3530,7 +3527,7 @@
         <v>166</v>
       </c>
       <c r="C163" t="n">
-        <v>0.00880533662757085</v>
+        <v>0.00880743994783173</v>
       </c>
       <c r="D163"/>
     </row>
@@ -3542,10 +3539,10 @@
         <v>167</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0087177429041272</v>
+        <v>0.00871801862568142</v>
       </c>
       <c r="D164" t="n">
-        <v>0.00164723672236698</v>
+        <v>0.00164689990286649</v>
       </c>
     </row>
     <row r="165">
@@ -3556,10 +3553,10 @@
         <v>168</v>
       </c>
       <c r="C165" t="n">
-        <v>0.00847237584434437</v>
+        <v>0.00847597594918435</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00299694118503875</v>
+        <v>0.0029978767958389</v>
       </c>
     </row>
     <row r="166">
@@ -3570,10 +3567,10 @@
         <v>169</v>
       </c>
       <c r="C166" t="n">
-        <v>0.00829950529628536</v>
+        <v>0.00829750682753266</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00488196017629464</v>
+        <v>0.00488004694521971</v>
       </c>
     </row>
     <row r="167">
@@ -3584,10 +3581,10 @@
         <v>170</v>
       </c>
       <c r="C167" t="n">
-        <v>0.00751019018255811</v>
+        <v>0.00751056931079806</v>
       </c>
       <c r="D167" t="n">
-        <v>0.00155233406502311</v>
+        <v>0.00155267126757225</v>
       </c>
     </row>
     <row r="168">
@@ -3598,10 +3595,10 @@
         <v>171</v>
       </c>
       <c r="C168" t="n">
-        <v>0.00742805238216173</v>
+        <v>0.00742824491897714</v>
       </c>
       <c r="D168" t="n">
-        <v>0.00249558133931395</v>
+        <v>0.00249563702895372</v>
       </c>
     </row>
     <row r="169">
@@ -3612,7 +3609,7 @@
         <v>172</v>
       </c>
       <c r="C169" t="n">
-        <v>0.00730959158723154</v>
+        <v>0.00730789592149665</v>
       </c>
       <c r="D169"/>
     </row>
@@ -3624,10 +3621,10 @@
         <v>173</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0072583208583217</v>
+        <v>0.00725821740919093</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00165758289577762</v>
+        <v>0.00165753410433041</v>
       </c>
     </row>
     <row r="171">
@@ -3638,10 +3635,10 @@
         <v>174</v>
       </c>
       <c r="C171" t="n">
-        <v>0.00652079964420746</v>
+        <v>0.00652192956364923</v>
       </c>
       <c r="D171" t="n">
-        <v>0.000604458007978263</v>
+        <v>0.000604862213706371</v>
       </c>
     </row>
     <row r="172">
@@ -3652,7 +3649,7 @@
         <v>175</v>
       </c>
       <c r="C172" t="n">
-        <v>0.00650465609108132</v>
+        <v>0.00650168463607803</v>
       </c>
       <c r="D172"/>
     </row>
@@ -3664,10 +3661,10 @@
         <v>176</v>
       </c>
       <c r="C173" t="n">
-        <v>0.00542079587147404</v>
+        <v>0.00542369827130868</v>
       </c>
       <c r="D173" t="n">
-        <v>0.00118258111092811</v>
+        <v>0.00118306418578259</v>
       </c>
     </row>
     <row r="174">
@@ -3678,7 +3675,7 @@
         <v>177</v>
       </c>
       <c r="C174" t="n">
-        <v>0.00527625128005765</v>
+        <v>0.00527570859780846</v>
       </c>
       <c r="D174"/>
     </row>
@@ -3690,10 +3687,10 @@
         <v>178</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0052567444866969</v>
+        <v>0.0052588253740775</v>
       </c>
       <c r="D175" t="n">
-        <v>0.000263216582366931</v>
+        <v>0.000263776214123878</v>
       </c>
     </row>
     <row r="176">
@@ -3704,10 +3701,10 @@
         <v>179</v>
       </c>
       <c r="C176" t="n">
-        <v>0.00460920863352648</v>
+        <v>0.00460949360120326</v>
       </c>
       <c r="D176" t="n">
-        <v>0.000478895956824243</v>
+        <v>0.000479108282563972</v>
       </c>
     </row>
     <row r="177">
@@ -3718,10 +3715,10 @@
         <v>180</v>
       </c>
       <c r="C177" t="n">
-        <v>0.00445009000109344</v>
+        <v>0.00445089588447386</v>
       </c>
       <c r="D177" t="n">
-        <v>0.00229414130414443</v>
+        <v>0.00229383283233085</v>
       </c>
     </row>
     <row r="178">
@@ -3732,7 +3729,7 @@
         <v>181</v>
       </c>
       <c r="C178" t="n">
-        <v>0.00418940151357515</v>
+        <v>0.00418838416681624</v>
       </c>
       <c r="D178"/>
     </row>
@@ -3744,10 +3741,10 @@
         <v>182</v>
       </c>
       <c r="C179" t="n">
-        <v>0.00400591807410915</v>
+        <v>0.00400558218243712</v>
       </c>
       <c r="D179" t="n">
-        <v>0.00163517682772478</v>
+        <v>0.00163411290226959</v>
       </c>
     </row>
     <row r="180">
@@ -3758,10 +3755,10 @@
         <v>183</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00373738202604344</v>
+        <v>0.00373940994282013</v>
       </c>
       <c r="D180" t="n">
-        <v>0.000765827555281527</v>
+        <v>0.000766056267798751</v>
       </c>
     </row>
     <row r="181">
@@ -3772,10 +3769,10 @@
         <v>184</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00372960920416789</v>
+        <v>0.00373022128565682</v>
       </c>
       <c r="D181" t="n">
-        <v>0.000423355937249699</v>
+        <v>0.000423316316465792</v>
       </c>
     </row>
     <row r="182">
@@ -3786,7 +3783,7 @@
         <v>185</v>
       </c>
       <c r="C182" t="n">
-        <v>0.00370255380494725</v>
+        <v>0.00370190826886904</v>
       </c>
       <c r="D182"/>
     </row>
@@ -3798,10 +3795,10 @@
         <v>186</v>
       </c>
       <c r="C183" t="n">
-        <v>0.00362475084751991</v>
+        <v>0.00362309498994793</v>
       </c>
       <c r="D183" t="n">
-        <v>0.000778057790422294</v>
+        <v>0.000777702358300775</v>
       </c>
     </row>
     <row r="184">
@@ -3812,10 +3809,10 @@
         <v>187</v>
       </c>
       <c r="C184" t="n">
-        <v>0.00358528882876715</v>
+        <v>0.00358551861146706</v>
       </c>
       <c r="D184" t="n">
-        <v>0.000338815391567233</v>
+        <v>0.000338416431745612</v>
       </c>
     </row>
     <row r="185">
@@ -3826,10 +3823,10 @@
         <v>188</v>
       </c>
       <c r="C185" t="n">
-        <v>0.00339769476234774</v>
+        <v>0.00339711378735422</v>
       </c>
       <c r="D185" t="n">
-        <v>0.00028522185253323</v>
+        <v>0.000284404844539178</v>
       </c>
     </row>
     <row r="186">
@@ -3840,7 +3837,7 @@
         <v>189</v>
       </c>
       <c r="C186" t="n">
-        <v>0.00311996585764075</v>
+        <v>0.00311854059579324</v>
       </c>
       <c r="D186"/>
     </row>
@@ -3852,7 +3849,7 @@
         <v>190</v>
       </c>
       <c r="C187" t="n">
-        <v>0.00305726011193323</v>
+        <v>0.00305638642701374</v>
       </c>
       <c r="D187"/>
     </row>
@@ -3864,10 +3861,10 @@
         <v>191</v>
       </c>
       <c r="C188" t="n">
-        <v>0.002986258373647</v>
+        <v>0.00298638828260703</v>
       </c>
       <c r="D188" t="n">
-        <v>0.000619592551250618</v>
+        <v>0.000618253027579224</v>
       </c>
     </row>
     <row r="189">
@@ -3878,10 +3875,10 @@
         <v>192</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00271548016542487</v>
+        <v>0.00271573377120306</v>
       </c>
       <c r="D189" t="n">
-        <v>0.000838276260383664</v>
+        <v>0.000838329018581751</v>
       </c>
     </row>
     <row r="190">
@@ -3892,7 +3889,7 @@
         <v>193</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00253401467009964</v>
+        <v>0.00253285708229416</v>
       </c>
       <c r="D190"/>
     </row>
@@ -3904,7 +3901,7 @@
         <v>194</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00220964883413939</v>
+        <v>0.00221095526345902</v>
       </c>
       <c r="D191"/>
     </row>
@@ -3916,10 +3913,10 @@
         <v>195</v>
       </c>
       <c r="C192" t="n">
-        <v>0.00218505981109079</v>
+        <v>0.00218406163273712</v>
       </c>
       <c r="D192" t="n">
-        <v>0.0000467178279858024</v>
+        <v>0.0000466964863619305</v>
       </c>
     </row>
     <row r="193">
@@ -3930,10 +3927,10 @@
         <v>196</v>
       </c>
       <c r="C193" t="n">
-        <v>0.002015178809907</v>
+        <v>0.00201515469089765</v>
       </c>
       <c r="D193" t="n">
-        <v>0.000572399089269485</v>
+        <v>0.000571503717137699</v>
       </c>
     </row>
     <row r="194">
@@ -3944,7 +3941,7 @@
         <v>197</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00201293664975059</v>
+        <v>0.00201328707765308</v>
       </c>
       <c r="D194"/>
     </row>
@@ -3956,10 +3953,10 @@
         <v>198</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00199761522201514</v>
+        <v>0.00199834617169647</v>
       </c>
       <c r="D195" t="n">
-        <v>0.000186058412341193</v>
+        <v>0.000185877455545797</v>
       </c>
     </row>
     <row r="196">
@@ -3970,7 +3967,7 @@
         <v>199</v>
       </c>
       <c r="C196" t="n">
-        <v>0.001954640485684</v>
+        <v>0.00195471872630317</v>
       </c>
       <c r="D196"/>
     </row>
@@ -3982,7 +3979,7 @@
         <v>200</v>
       </c>
       <c r="C197" t="n">
-        <v>0.00193124728138548</v>
+        <v>0.0019303650495939</v>
       </c>
       <c r="D197"/>
     </row>
@@ -3994,11 +3991,9 @@
         <v>201</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00190180024466467</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0.000474233940753386</v>
-      </c>
+        <v>0.00187605485644162</v>
+      </c>
+      <c r="D198"/>
     </row>
     <row r="199">
       <c r="A199" t="s">
@@ -4008,7 +4003,7 @@
         <v>202</v>
       </c>
       <c r="C199" t="n">
-        <v>0.00187549223216282</v>
+        <v>0.0018651479950933</v>
       </c>
       <c r="D199"/>
     </row>
@@ -4020,9 +4015,11 @@
         <v>203</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00186540251145899</v>
-      </c>
-      <c r="D200"/>
+        <v>0.00178379476215956</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.000801552583773679</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
@@ -4032,11 +4029,9 @@
         <v>204</v>
       </c>
       <c r="C201" t="n">
-        <v>0.00178333944973448</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.000801020496358377</v>
-      </c>
+        <v>0.00177542785482386</v>
+      </c>
+      <c r="D201"/>
     </row>
     <row r="202">
       <c r="A202" t="s">
@@ -4046,9 +4041,11 @@
         <v>205</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00177541715051518</v>
-      </c>
-      <c r="D202"/>
+        <v>0.00172358291115443</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.00017928492614524</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
@@ -4058,10 +4055,10 @@
         <v>206</v>
       </c>
       <c r="C203" t="n">
-        <v>0.00172227795480832</v>
+        <v>0.00168077721558874</v>
       </c>
       <c r="D203" t="n">
-        <v>0.00017926116801792</v>
+        <v>0.000589358256040789</v>
       </c>
     </row>
     <row r="204">
@@ -4072,10 +4069,10 @@
         <v>207</v>
       </c>
       <c r="C204" t="n">
-        <v>0.00168064851457103</v>
+        <v>0.00166710628663845</v>
       </c>
       <c r="D204" t="n">
-        <v>0.000589627609544792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -4086,11 +4083,9 @@
         <v>208</v>
       </c>
       <c r="C205" t="n">
-        <v>0.0016663734282419</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0</v>
-      </c>
+        <v>0.00165941172007079</v>
+      </c>
+      <c r="D205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
@@ -4100,9 +4095,11 @@
         <v>209</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00165785321964755</v>
-      </c>
-      <c r="D206"/>
+        <v>0.00151224379639819</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.000172560839438855</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
@@ -4112,11 +4109,9 @@
         <v>210</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00151293493487176</v>
-      </c>
-      <c r="D207" t="n">
-        <v>0.00017263970465586</v>
-      </c>
+        <v>0.00145868064854375</v>
+      </c>
+      <c r="D207"/>
     </row>
     <row r="208">
       <c r="A208" t="s">
@@ -4126,7 +4121,7 @@
         <v>211</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00145807674971166</v>
+        <v>0.00139600354805577</v>
       </c>
       <c r="D208"/>
     </row>
@@ -4138,7 +4133,7 @@
         <v>212</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00139537100400414</v>
+        <v>0.00138599314106484</v>
       </c>
       <c r="D209"/>
     </row>
@@ -4150,9 +4145,11 @@
         <v>213</v>
       </c>
       <c r="C210" t="n">
-        <v>0.00138662657939415</v>
-      </c>
-      <c r="D210"/>
+        <v>0.0013245113130534</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.000347159851097972</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
@@ -4162,11 +4159,9 @@
         <v>214</v>
       </c>
       <c r="C211" t="n">
-        <v>0.00132474295907731</v>
-      </c>
-      <c r="D211" t="n">
-        <v>0.000347582754143237</v>
-      </c>
+        <v>0.00128932547952558</v>
+      </c>
+      <c r="D211"/>
     </row>
     <row r="212">
       <c r="A212" t="s">
@@ -4176,7 +4171,7 @@
         <v>215</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00128871891923103</v>
+        <v>0.00127386164186049</v>
       </c>
       <c r="D212"/>
     </row>
@@ -4188,7 +4183,7 @@
         <v>216</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00127444383290191</v>
+        <v>0.00126646589341197</v>
       </c>
       <c r="D213"/>
     </row>
@@ -4200,9 +4195,11 @@
         <v>217</v>
       </c>
       <c r="C214" t="n">
-        <v>0.00126704470438576</v>
-      </c>
-      <c r="D214"/>
+        <v>0.00125832309966562</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.00000570500059625399</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
@@ -4212,11 +4209,9 @@
         <v>218</v>
       </c>
       <c r="C215" t="n">
-        <v>0.00125837501844765</v>
-      </c>
-      <c r="D215" t="n">
-        <v>0.00000607754549589062</v>
-      </c>
+        <v>0.00124091694422617</v>
+      </c>
+      <c r="D215"/>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -4226,9 +4221,11 @@
         <v>219</v>
       </c>
       <c r="C216" t="n">
-        <v>0.00124148407860272</v>
-      </c>
-      <c r="D216"/>
+        <v>0.0012363599679094</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.000275107806530468</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
@@ -4238,10 +4235,10 @@
         <v>220</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00123647658758674</v>
+        <v>0.00120692638317488</v>
       </c>
       <c r="D217" t="n">
-        <v>0.000275550627961508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -4252,11 +4249,9 @@
         <v>221</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00120568425477208</v>
-      </c>
-      <c r="D218" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0011293083767303</v>
+      </c>
+      <c r="D218"/>
     </row>
     <row r="219">
       <c r="A219" t="s">
@@ -4266,9 +4261,11 @@
         <v>222</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00112982450281364</v>
-      </c>
-      <c r="D219"/>
+        <v>0.00110973578992714</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.000385246012485926</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
@@ -4278,11 +4275,9 @@
         <v>223</v>
       </c>
       <c r="C220" t="n">
-        <v>0.00110986927742161</v>
-      </c>
-      <c r="D220" t="n">
-        <v>0.000385686321991386</v>
-      </c>
+        <v>0.00110308708677645</v>
+      </c>
+      <c r="D220"/>
     </row>
     <row r="221">
       <c r="A221" t="s">
@@ -4292,9 +4287,11 @@
         <v>224</v>
       </c>
       <c r="C221" t="n">
-        <v>0.00110359122898367</v>
-      </c>
-      <c r="D221"/>
+        <v>0.000876209429825342</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.0000204429188032432</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
@@ -4304,11 +4301,9 @@
         <v>225</v>
       </c>
       <c r="C222" t="n">
-        <v>0.000875563541077049</v>
-      </c>
-      <c r="D222" t="n">
-        <v>0.0000203465653558076</v>
-      </c>
+        <v>0.000833553143319223</v>
+      </c>
+      <c r="D222"/>
     </row>
     <row r="223">
       <c r="A223" t="s">
@@ -4318,9 +4313,11 @@
         <v>226</v>
       </c>
       <c r="C223" t="n">
-        <v>0.000833186714120951</v>
-      </c>
-      <c r="D223"/>
+        <v>0.000827277962817447</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
@@ -4330,11 +4327,9 @@
         <v>227</v>
       </c>
       <c r="C224" t="n">
-        <v>0.000827656052401813</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0</v>
-      </c>
+        <v>0.000791494493051368</v>
+      </c>
+      <c r="D224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
@@ -4344,7 +4339,7 @@
         <v>228</v>
       </c>
       <c r="C225" t="n">
-        <v>0.000791856228571177</v>
+        <v>0.000754291637219411</v>
       </c>
       <c r="D225"/>
     </row>
@@ -4356,7 +4351,7 @@
         <v>229</v>
       </c>
       <c r="C226" t="n">
-        <v>0.000753590028568492</v>
+        <v>0.000730236778629271</v>
       </c>
       <c r="D226"/>
     </row>
@@ -4368,7 +4363,7 @@
         <v>230</v>
       </c>
       <c r="C227" t="n">
-        <v>0.000730570517629377</v>
+        <v>0.000698039126292778</v>
       </c>
       <c r="D227"/>
     </row>
@@ -4380,9 +4375,11 @@
         <v>231</v>
       </c>
       <c r="C228" t="n">
-        <v>0.00069768550200207</v>
-      </c>
-      <c r="D228"/>
+        <v>0.00065075115894011</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.0000334376423835995</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
@@ -4392,11 +4389,9 @@
         <v>232</v>
       </c>
       <c r="C229" t="n">
-        <v>0.000650226445358116</v>
-      </c>
-      <c r="D229" t="n">
-        <v>0.0000335057725599533</v>
-      </c>
+        <v>0.000633195594441095</v>
+      </c>
+      <c r="D229"/>
     </row>
     <row r="230">
       <c r="A230" t="s">
@@ -4406,7 +4401,7 @@
         <v>233</v>
       </c>
       <c r="C230" t="n">
-        <v>0.000633484982856941</v>
+        <v>0.000633195594441095</v>
       </c>
       <c r="D230"/>
     </row>
@@ -4418,7 +4413,7 @@
         <v>234</v>
       </c>
       <c r="C231" t="n">
-        <v>0.000633484982856941</v>
+        <v>0.000633195594441095</v>
       </c>
       <c r="D231"/>
     </row>
@@ -4430,7 +4425,7 @@
         <v>235</v>
       </c>
       <c r="C232" t="n">
-        <v>0.000633484982856941</v>
+        <v>0.000625127505224526</v>
       </c>
       <c r="D232"/>
     </row>
@@ -4442,7 +4437,7 @@
         <v>236</v>
       </c>
       <c r="C233" t="n">
-        <v>0.000624890035590713</v>
+        <v>0.000564840949689608</v>
       </c>
       <c r="D233"/>
     </row>
@@ -4454,7 +4449,7 @@
         <v>237</v>
       </c>
       <c r="C234" t="n">
-        <v>0.000564501188711477</v>
+        <v>0.000551543543388226</v>
       </c>
       <c r="D234"/>
     </row>
@@ -4466,7 +4461,7 @@
         <v>238</v>
       </c>
       <c r="C235" t="n">
-        <v>0.000551795614491835</v>
+        <v>0.000523529344719584</v>
       </c>
       <c r="D235"/>
     </row>
@@ -4478,7 +4473,7 @@
         <v>239</v>
       </c>
       <c r="C236" t="n">
-        <v>0.000523245441833582</v>
+        <v>0.000523529344719584</v>
       </c>
       <c r="D236"/>
     </row>
@@ -4490,7 +4485,7 @@
         <v>240</v>
       </c>
       <c r="C237" t="n">
-        <v>0.000523245441833582</v>
+        <v>0.000521885845064357</v>
       </c>
       <c r="D237"/>
     </row>
@@ -4502,7 +4497,7 @@
         <v>241</v>
       </c>
       <c r="C238" t="n">
-        <v>0.000522124361755379</v>
+        <v>0.000474896695830821</v>
       </c>
       <c r="D238"/>
     </row>
@@ -4514,7 +4509,7 @@
         <v>242</v>
       </c>
       <c r="C239" t="n">
-        <v>0.000475113737142706</v>
+        <v>0.000474896695830821</v>
       </c>
       <c r="D239"/>
     </row>
@@ -4526,7 +4521,7 @@
         <v>243</v>
       </c>
       <c r="C240" t="n">
-        <v>0.000475113737142706</v>
+        <v>0.000474896695830821</v>
       </c>
       <c r="D240"/>
     </row>
@@ -4538,7 +4533,7 @@
         <v>244</v>
       </c>
       <c r="C241" t="n">
-        <v>0.000475113737142706</v>
+        <v>0.000474896695830821</v>
       </c>
       <c r="D241"/>
     </row>
@@ -4550,7 +4545,7 @@
         <v>245</v>
       </c>
       <c r="C242" t="n">
-        <v>0.000475113737142706</v>
+        <v>0.000453830018432002</v>
       </c>
       <c r="D242"/>
     </row>
@@ -4562,7 +4557,7 @@
         <v>246</v>
       </c>
       <c r="C243" t="n">
-        <v>0.000454037431672477</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D243"/>
     </row>
@@ -4574,7 +4569,7 @@
         <v>247</v>
       </c>
       <c r="C244" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D244"/>
     </row>
@@ -4586,7 +4581,7 @@
         <v>248</v>
       </c>
       <c r="C245" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.000413638981408723</v>
       </c>
       <c r="D245"/>
     </row>
@@ -4598,7 +4593,7 @@
         <v>249</v>
       </c>
       <c r="C246" t="n">
-        <v>0.000413828026200906</v>
+        <v>0.000361121696971242</v>
       </c>
       <c r="D246"/>
     </row>
@@ -4610,7 +4605,7 @@
         <v>250</v>
       </c>
       <c r="C247" t="n">
-        <v>0.000361286739869095</v>
+        <v>0.000349019563146389</v>
       </c>
       <c r="D247"/>
     </row>
@@ -4622,7 +4617,7 @@
         <v>251</v>
       </c>
       <c r="C248" t="n">
-        <v>0.000348805381665095</v>
+        <v>0.000302553345621335</v>
       </c>
       <c r="D248"/>
     </row>
@@ -4634,7 +4629,7 @@
         <v>252</v>
       </c>
       <c r="C249" t="n">
-        <v>0.000302691621114985</v>
+        <v>0.000301731595793721</v>
       </c>
       <c r="D249"/>
     </row>
@@ -4646,7 +4641,7 @@
         <v>253</v>
       </c>
       <c r="C250" t="n">
-        <v>0.000301421063693021</v>
+        <v>0.000301731595793721</v>
       </c>
       <c r="D250"/>
     </row>
@@ -4658,21 +4653,9 @@
         <v>254</v>
       </c>
       <c r="C251" t="n">
-        <v>0.000301421063693021</v>
+        <v>0.000275734419429221</v>
       </c>
       <c r="D251"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>4</v>
-      </c>
-      <c r="B252" t="s">
-        <v>255</v>
-      </c>
-      <c r="C252" t="n">
-        <v>0.000275860437909978</v>
-      </c>
-      <c r="D252"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4701,3689 +4684,3675 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1787729386202</v>
+        <v>11.3906787774023</v>
       </c>
       <c r="D2" t="n">
-        <v>2.94460434793981</v>
+        <v>3.00054024635649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>9.38832420741317</v>
+        <v>9.07055414780989</v>
       </c>
       <c r="D3" t="n">
-        <v>0.651672941584879</v>
+        <v>0.622468519214623</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8.28770331205634</v>
+        <v>8.40161069868793</v>
       </c>
       <c r="D4" t="n">
-        <v>0.668281225283254</v>
+        <v>0.677190845957553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.60394360681681</v>
+        <v>6.67559535364527</v>
       </c>
       <c r="D5" t="n">
-        <v>0.26760773674499</v>
+        <v>0.270837605390523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.03520600865828</v>
+        <v>5.10531923308543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.119574483856693</v>
+        <v>0.121253355401514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.83024898486416</v>
+        <v>4.89377513701579</v>
       </c>
       <c r="D7" t="n">
-        <v>0.899399327704086</v>
+        <v>0.911340709383308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>3.76342057458063</v>
+        <v>3.79913331343181</v>
       </c>
       <c r="D8" t="n">
-        <v>0.401921415916977</v>
+        <v>0.404704747119783</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5685510748317</v>
+        <v>3.61662261318242</v>
       </c>
       <c r="D9" t="n">
-        <v>0.168892102245766</v>
+        <v>0.171165588023564</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.15034892229709</v>
+        <v>3.193250233692</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0646529388543776</v>
+        <v>0.0655202488941631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>3.06168456798141</v>
+        <v>3.10491048095972</v>
       </c>
       <c r="D11" t="n">
-        <v>0.282227908809566</v>
+        <v>0.286215234981732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>2.7800674721115</v>
+        <v>2.81805174549163</v>
       </c>
       <c r="D12" t="n">
-        <v>0.377052605584892</v>
+        <v>0.38202120658855</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>2.52519197337837</v>
+        <v>2.56269720780837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.355756963063507</v>
+        <v>0.361177924863553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s">
         <v>89</v>
       </c>
       <c r="C14" t="n">
-        <v>1.93006326217037</v>
+        <v>1.95573637518033</v>
       </c>
       <c r="D14" t="n">
-        <v>0.217838813297085</v>
+        <v>0.220674305153084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C15" t="n">
-        <v>1.55873020044419</v>
+        <v>1.57898331571465</v>
       </c>
       <c r="D15" t="n">
-        <v>0.43660991644259</v>
+        <v>0.442282125524756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="n">
-        <v>1.54203226842784</v>
+        <v>1.56319186646503</v>
       </c>
       <c r="D16" t="n">
-        <v>0.096475549753605</v>
+        <v>0.0978013096692827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>1.508592975179</v>
+        <v>1.51460726307645</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0393988585022581</v>
+        <v>0.0397095256164362</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>1.33412334706155</v>
+        <v>1.35070887551546</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0757845924425917</v>
+        <v>0.0768304756670209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1766861647843</v>
+        <v>1.19342317619039</v>
       </c>
       <c r="D19" t="n">
-        <v>0.120847864310866</v>
+        <v>0.122567720364319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>1.02408054009784</v>
+        <v>1.02614329867811</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0442761278290968</v>
+        <v>0.0438677581148614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="n">
-        <v>0.99275607206245</v>
+        <v>1.00738908094048</v>
       </c>
       <c r="D21" t="n">
-        <v>0.159892148546546</v>
+        <v>0.162304710061375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>0.954029500925675</v>
+        <v>0.936499760659141</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0441821896441161</v>
+        <v>0.0425447707957961</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.817122334692145</v>
+        <v>0.798781200573575</v>
       </c>
       <c r="D23" t="n">
-        <v>0.465312954881943</v>
+        <v>0.0299539993786084</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0.788172121277482</v>
+        <v>0.77743798470254</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0295282071946689</v>
+        <v>0.0698965284714301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="C25" t="n">
-        <v>0.766088278925184</v>
+        <v>0.751293415843645</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0688765463767698</v>
+        <v>0.371942557243908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="C26" t="n">
-        <v>0.741628892826351</v>
+        <v>0.728314693496191</v>
       </c>
       <c r="D26" t="n">
-        <v>0.367176866375357</v>
+        <v>0.0885673448298542</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>0.718768824853531</v>
+        <v>0.705470331144227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.087433555920052</v>
+        <v>0.0321033178827312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C28" t="n">
-        <v>0.695440746917527</v>
+        <v>0.694188589535885</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0316640313558494</v>
+        <v>0.0174201584808455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>0.684359564698681</v>
+        <v>0.664398163650344</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0171782647898468</v>
+        <v>0.10257599733231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C30" t="n">
-        <v>0.655156109680629</v>
+        <v>0.655975242905002</v>
       </c>
       <c r="D30" t="n">
-        <v>0.101133634761853</v>
+        <v>0.0800591919133054</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
-        <v>0.647081369379292</v>
+        <v>0.629742164761821</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0789661974186818</v>
+        <v>0.0266337631017512</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.622926102382447</v>
+        <v>0.6250514338696</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0263117448123564</v>
+        <v>0.0728959377836819</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C33" t="n">
-        <v>0.618749277466473</v>
+        <v>0.600338132686204</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0720040262147317</v>
+        <v>0.254794237224404</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="C34" t="n">
-        <v>0.604900399429963</v>
+        <v>0.578208257904209</v>
       </c>
       <c r="D34" t="n">
-        <v>0.25665594684008</v>
+        <v>0.0626648154152822</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C35" t="n">
-        <v>0.57028969188201</v>
+        <v>0.565248583401867</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0618314184774101</v>
+        <v>0.223054136267222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C36" t="n">
-        <v>0.55787953554294</v>
+        <v>0.554843054688519</v>
       </c>
       <c r="D36" t="n">
-        <v>0.220142187115431</v>
+        <v>0.0401119412910551</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C37" t="n">
-        <v>0.547181137747676</v>
+        <v>0.542260545814985</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0395523162202596</v>
+        <v>0.0756981320273108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C38" t="n">
-        <v>0.535356674234541</v>
+        <v>0.530417713383144</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0747121370460776</v>
+        <v>0.050888523844355</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="C39" t="n">
-        <v>0.522668467782067</v>
+        <v>0.484635342954498</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0501102489957398</v>
+        <v>0.0780168403652889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="C40" t="n">
-        <v>0.47770341579368</v>
+        <v>0.406784578837727</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0768589214136416</v>
+        <v>0.0288408938510205</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C41" t="n">
-        <v>0.401368976897267</v>
+        <v>0.365519025812538</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0284640790427565</v>
+        <v>0.0305158496605616</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>0.360273680057125</v>
+        <v>0.363375069772194</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0300826102281944</v>
+        <v>0.0262678913626295</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="C43" t="n">
-        <v>0.358576101897218</v>
+        <v>0.343831233140974</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0259373157602803</v>
+        <v>0.0487533868528763</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C44" t="n">
-        <v>0.344811819161026</v>
+        <v>0.316590309934431</v>
       </c>
       <c r="D44" t="n">
-        <v>0.048885474600544</v>
+        <v>0.070910539926363</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>0.315478735381059</v>
+        <v>0.294538120186546</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0697762775302625</v>
+        <v>0.0154624196317962</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="C46" t="n">
-        <v>0.290606628492632</v>
+        <v>0.27317998832465</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0152269898352527</v>
+        <v>0.0321272128800466</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>255</v>
+      </c>
+      <c r="B47" t="s">
         <v>256</v>
       </c>
-      <c r="B47" t="s">
-        <v>257</v>
-      </c>
       <c r="C47" t="n">
-        <v>0.268130777305405</v>
+        <v>0.271614447711974</v>
       </c>
       <c r="D47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s">
-        <v>238</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>0.268068498205206</v>
+        <v>0.257018309091778</v>
       </c>
       <c r="D48" t="n">
-        <v>0.031431416429541</v>
+        <v>0.031736171148511</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="C49" t="n">
-        <v>0.253257903667865</v>
+        <v>0.254295966643203</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0312647191932013</v>
+        <v>0.119599662170047</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C50" t="n">
-        <v>0.251029148380127</v>
+        <v>0.253337831876229</v>
       </c>
       <c r="D50" t="n">
-        <v>0.118066558167185</v>
+        <v>0.139043368674031</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C51" t="n">
-        <v>0.24980593987073</v>
+        <v>0.231083521746359</v>
       </c>
       <c r="D51" t="n">
-        <v>0.137157739177543</v>
+        <v>0.0204134085067861</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="C52" t="n">
-        <v>0.227903405901672</v>
+        <v>0.228802013572404</v>
       </c>
       <c r="D52" t="n">
-        <v>0.020137221710092</v>
+        <v>0.160896730087107</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>189</v>
       </c>
       <c r="C53" t="n">
-        <v>0.225867446540496</v>
+        <v>0.227459487336691</v>
       </c>
       <c r="D53" t="n">
-        <v>0.158833102095888</v>
+        <v>0.0898771701022783</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="C54" t="n">
-        <v>0.223413753122689</v>
+        <v>0.226455734014013</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0882127420494344</v>
+        <v>0.0676192981252538</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B55" t="s">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="C55" t="n">
-        <v>0.22334448409588</v>
+        <v>0.222032968607399</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0666905620593824</v>
+        <v>0.0235499256434138</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C56" t="n">
-        <v>0.219059687731585</v>
+        <v>0.208388580477933</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0232389892069411</v>
+        <v>0.0770989254009204</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C57" t="n">
-        <v>0.205632640307053</v>
+        <v>0.203420859055054</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0760739847336768</v>
+        <v>0.113602270817737</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B58" t="s">
         <v>47</v>
       </c>
       <c r="C58" t="n">
-        <v>0.201740253839049</v>
+        <v>0.200479419853574</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0127362299980534</v>
+        <v>0.0123753696026022</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>225</v>
       </c>
       <c r="C59" t="n">
-        <v>0.200632063999063</v>
+        <v>0.199562695823871</v>
       </c>
       <c r="D59" t="n">
-        <v>0.112044905946011</v>
+        <v>0.0879461186873697</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
       <c r="C60" t="n">
-        <v>0.196791930097187</v>
+        <v>0.174760333986876</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0867203745537359</v>
+        <v>0.0233813615690755</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C61" t="n">
-        <v>0.172200451573782</v>
+        <v>0.162850205479541</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0230298095020847</v>
+        <v>0.014934706828791</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="C62" t="n">
-        <v>0.160748688655679</v>
+        <v>0.159573969027961</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0147424865213106</v>
+        <v>0.046071046293777</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="C63" t="n">
-        <v>0.160407385435909</v>
-      </c>
-      <c r="D63"/>
+        <v>0.153076516978245</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.0184587006514247</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="C64" t="n">
-        <v>0.157461647020388</v>
+        <v>0.152784871631663</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0454694997861624</v>
+        <v>0.0464613691694384</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="C65" t="n">
-        <v>0.15645068591365</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.0477361676717595</v>
-      </c>
+        <v>0.1517910429566</v>
+      </c>
+      <c r="D65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C66" t="n">
-        <v>0.150575452067804</v>
+        <v>0.144934069096059</v>
       </c>
       <c r="D66" t="n">
-        <v>0.018133828019347</v>
+        <v>0.043710967608872</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="C67" t="n">
-        <v>0.142747335857368</v>
+        <v>0.144215083513282</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0430225237537668</v>
+        <v>0.0409931333226437</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B68" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="C68" t="n">
-        <v>0.142220369873847</v>
+        <v>0.1406423844885</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0404313762934247</v>
+        <v>0.0375469334006258</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C69" t="n">
-        <v>0.138638720020316</v>
+        <v>0.135025643346586</v>
       </c>
       <c r="D69" t="n">
-        <v>0.03702259070827</v>
+        <v>0.0108159852131835</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C70" t="n">
-        <v>0.133216542278269</v>
+        <v>0.135023699044275</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0106745505931504</v>
+        <v>0.0362715686015914</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="C71" t="n">
-        <v>0.133172998473161</v>
+        <v>0.131996507405069</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0357747273362706</v>
+        <v>0.0204959555924036</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C72" t="n">
-        <v>0.130250407027724</v>
+        <v>0.129277821405616</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0202301973681645</v>
+        <v>0.0158644449057194</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C73" t="n">
-        <v>0.127545334077143</v>
+        <v>0.128980575307602</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0156581949147364</v>
+        <v>0.00813957118733485</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C74" t="n">
-        <v>0.127142066876816</v>
+        <v>0.125255669333286</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00802171919862632</v>
+        <v>0.0133153589987534</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="C75" t="n">
-        <v>0.123150876077353</v>
+        <v>0.119836173307861</v>
       </c>
       <c r="D75" t="n">
-        <v>0.013049549729315</v>
+        <v>0.0172100880035607</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
-        <v>0.118151502953452</v>
+        <v>0.116360950573543</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0169613560993871</v>
+        <v>0.0249510391309751</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="C77" t="n">
-        <v>0.114685645244818</v>
+        <v>0.105749557970777</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0245655527752233</v>
+        <v>0.0514825495843906</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="C78" t="n">
-        <v>0.104390428708162</v>
+        <v>0.104478448570681</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0508227110452255</v>
+        <v>0.0585564615459557</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="C79" t="n">
-        <v>0.102923804598766</v>
+        <v>0.0986092963616454</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0576833500162469</v>
+        <v>0.00231903468806524</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0976664344296023</v>
+        <v>0.0968053320507096</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00231007176757483</v>
+        <v>0.0249879989122972</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0954844027906346</v>
+        <v>0.0966898056701383</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0246621407321716</v>
+        <v>0.00791636611171422</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0953619931332502</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.00780962174929297</v>
-      </c>
+        <v>0.0964860892190931</v>
+      </c>
+      <c r="D82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0952485787092894</v>
-      </c>
-      <c r="D83"/>
+        <v>0.0954825390324774</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.0103303942610915</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0941089914940425</v>
+        <v>0.0928533199587465</v>
       </c>
       <c r="D84" t="n">
-        <v>0.010175590735565</v>
+        <v>0.0102599425461149</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0916109235011632</v>
+        <v>0.0900956608547697</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0101276294945725</v>
+        <v>0.00800482913878275</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0916016417953377</v>
+        <v>0.089791624208388</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00845852166798351</v>
+        <v>0.00647576319463214</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0885522290175251</v>
+        <v>0.0893265006646057</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00638457334892884</v>
+        <v>0.00268695191490044</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0880873129562823</v>
+        <v>0.0866511987241711</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00265116003204996</v>
+        <v>0.00449311960313286</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0870527178763768</v>
+        <v>0.0825760571590194</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00465308293650732</v>
+        <v>0.0174269030277859</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B90" t="s">
         <v>196</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0844988164123432</v>
+        <v>0.081319080224971</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0271782135457512</v>
+        <v>0.0256279674832054</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>98</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0814889368260098</v>
+        <v>0.0806355563947833</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0172043778529389</v>
+        <v>0.0414863777516161</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0800573482913811</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.0329610989098214</v>
-      </c>
+        <v>0.080520581383524</v>
+      </c>
+      <c r="D92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0795968725523695</v>
+        <v>0.0800551096064921</v>
       </c>
       <c r="D93" t="n">
-        <v>0.040953391633717</v>
+        <v>0.0327873691851631</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B94" t="s">
         <v>259</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0794332681635743</v>
+        <v>0.0788910819306627</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
         <v>83</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0778887522080682</v>
+        <v>0.0779404631979937</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0238310032125513</v>
+        <v>0.0241368480023159</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B96" t="s">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0778612222102338</v>
-      </c>
-      <c r="D96"/>
+        <v>0.0753397702312966</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.00198932341464744</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C97" t="n">
-        <v>0.074322915631129</v>
+        <v>0.0732281998831701</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00196222932438885</v>
+        <v>0.0060210408842954</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0721488479249375</v>
+        <v>0.0701732656617423</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00593200372372648</v>
+        <v>0.0364047096601004</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0687573298046294</v>
+        <v>0.0689928129843044</v>
       </c>
       <c r="D99" t="n">
-        <v>0.03564596445624</v>
+        <v>0.00698901142106945</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0681132539031614</v>
+        <v>0.0657791134204738</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0214019947972042</v>
+        <v>0.0201661849819414</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B101" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0679534882445532</v>
+        <v>0.065227105680904</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00688564056057069</v>
+        <v>0.0113945693159239</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C102" t="n">
-        <v>0.064305921091317</v>
+        <v>0.0630863707981193</v>
       </c>
       <c r="D102" t="n">
-        <v>0.011230154631991</v>
+        <v>0.00921785215264765</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0621992603413215</v>
+        <v>0.0612506592225904</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00909501397317871</v>
+        <v>0.0198458036605469</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B104" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0604233606267015</v>
+        <v>0.0589028126145765</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0195724390892119</v>
+        <v>0.0242130900712287</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B105" t="s">
         <v>263</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0581360790272306</v>
+        <v>0.0564972173259957</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0238987466958655</v>
+        <v>0.0287704174234449</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B106" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0563901443258622</v>
+        <v>0.0564363345461819</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0102407849022143</v>
+        <v>0.00858440577140692</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0557487039704928</v>
+        <v>0.0564133801711425</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0283878398361279</v>
+        <v>0.00364532629936192</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0556433394210288</v>
+        <v>0.0559530158151055</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00846373562979262</v>
+        <v>0.0181254687030527</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0554807949801211</v>
+        <v>0.0559304096733157</v>
       </c>
       <c r="D109" t="n">
-        <v>0.00357828738154653</v>
+        <v>0.00825682410273574</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0551314705330944</v>
+        <v>0.0547964171152686</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0178571239040387</v>
+        <v>0.00965221378338962</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B111" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0551313845913738</v>
+        <v>0.0480434779380598</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00814205723575119</v>
+        <v>0.00281141695943564</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0473639718829265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0.00277216827582102</v>
-      </c>
+        <v>0.0465844386609021</v>
+      </c>
+      <c r="D112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B113" t="s">
-        <v>265</v>
+        <v>122</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0458693021253724</v>
-      </c>
-      <c r="D113"/>
+        <v>0.045479726715263</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.00740045427368931</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0448807718077122</v>
+        <v>0.0445832582529146</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00730547812292862</v>
+        <v>0.0226782212574015</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B115" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0439688442103529</v>
+        <v>0.0429075888750372</v>
       </c>
       <c r="D115" t="n">
-        <v>0.022367660420083</v>
+        <v>0.02580339228734</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>265</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0433363417939266</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0.00872138921092517</v>
-      </c>
+        <v>0.0427288871790919</v>
+      </c>
+      <c r="D116"/>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B117" t="s">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0423572650655332</v>
+        <v>0.0425426114099667</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0254724433453463</v>
+        <v>0.0103062083657077</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B118" t="s">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0420873794155875</v>
-      </c>
-      <c r="D118"/>
+        <v>0.0423765041498838</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0239798555752528</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0418099595414685</v>
+        <v>0.0423196550718785</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0236734293086432</v>
+        <v>0.00826729851615446</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0417022172710678</v>
+        <v>0.0409619806898063</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0100825607986756</v>
+        <v>0.0089058572415679</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>133</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0404331731773468</v>
+        <v>0.040320883277201</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00878920177019924</v>
+        <v>0.00542102753250326</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0397822219382303</v>
+        <v>0.0401199236727156</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00534862034970084</v>
+        <v>0.0277118195817346</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B123" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0395744148578029</v>
+        <v>0.0399478093890762</v>
       </c>
       <c r="D123" t="n">
-        <v>0.027335124057544</v>
+        <v>0.00848851154521043</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B124" t="s">
-        <v>151</v>
+        <v>229</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0394125006561796</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0.00837427541305335</v>
-      </c>
+        <v>0.0398051208150322</v>
+      </c>
+      <c r="D124"/>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>94</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0392607848720683</v>
-      </c>
-      <c r="D125"/>
+        <v>0.0379277083078578</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.00432337429411864</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B126" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0372844404177529</v>
+        <v>0.0377640386805224</v>
       </c>
       <c r="D126" t="n">
-        <v>0.00425140321148285</v>
+        <v>0.00470575262805252</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B127" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C127" t="n">
-        <v>0.037239979900959</v>
+        <v>0.0369252608598659</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0046423246437133</v>
+        <v>0.00124252146338765</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B128" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0365133140059879</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0.00486818219747944</v>
-      </c>
+        <v>0.0366361402043441</v>
+      </c>
+      <c r="D128"/>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0364198953556882</v>
+        <v>0.036546760336934</v>
       </c>
       <c r="D129" t="n">
-        <v>0.00122572144273086</v>
+        <v>0.00490097469395058</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B130" t="s">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="C130" t="n">
-        <v>0.036158288758161</v>
-      </c>
-      <c r="D130"/>
+        <v>0.0352781756278973</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.00734905707440079</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B131" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0348180849197775</v>
+        <v>0.0322710944588589</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00725469252960738</v>
+        <v>0.00554832337401497</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B132" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0318192631681622</v>
+        <v>0.0320640988113795</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00546686492924663</v>
+        <v>0.0190962975707846</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B133" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0316024322070711</v>
+        <v>0.029043204390105</v>
       </c>
       <c r="D133" t="n">
-        <v>0.018821676170103</v>
+        <v>0.00349213504192394</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B134" t="s">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0298388221584979</v>
+        <v>0.0290004587587105</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0204139102438886</v>
+        <v>0.0061315527163196</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B135" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0286455786623522</v>
+        <v>0.028775267923937</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00344630300614833</v>
+        <v>0.0196517696672456</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B136" t="s">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0286237781125583</v>
+        <v>0.0284240746916651</v>
       </c>
       <c r="D136" t="n">
-        <v>0.00605336280539562</v>
+        <v>0.00718108046145556</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B137" t="s">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0279613966246011</v>
+        <v>0.0271115835737351</v>
       </c>
       <c r="D137" t="n">
-        <v>0.00707456156511684</v>
+        <v>0.00860439564409171</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B138" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0267576682385413</v>
+        <v>0.0265918454486327</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00849361648681226</v>
+        <v>0.0034928416871226</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B139" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C139" t="n">
-        <v>0.026197242278464</v>
+        <v>0.0262491258921024</v>
       </c>
       <c r="D139" t="n">
-        <v>0.00343924879521813</v>
+        <v>0.00912560058852466</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B140" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0258934382961188</v>
+        <v>0.0258992675539542</v>
       </c>
       <c r="D140" t="n">
-        <v>0.00900491434123902</v>
+        <v>0.0177135475636874</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B141" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0255653701013222</v>
+        <v>0.0257997599028668</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0174875726867815</v>
+        <v>0.00433423313538174</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B142" t="s">
-        <v>183</v>
+        <v>39</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0254236522040415</v>
+        <v>0.0250860268382721</v>
       </c>
       <c r="D142" t="n">
-        <v>0.00426833569194556</v>
+        <v>0.0011748484305198</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B143" t="s">
-        <v>39</v>
+        <v>268</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0247384102184029</v>
+        <v>0.0227285457770179</v>
       </c>
       <c r="D143" t="n">
-        <v>0.00115861941766982</v>
+        <v>0.0065813568791127</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B144" t="s">
         <v>269</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0224147752711152</v>
-      </c>
-      <c r="D144" t="n">
-        <v>0.00648642761748501</v>
-      </c>
+        <v>0.0223382053235979</v>
+      </c>
+      <c r="D144"/>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B145" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0220373478814501</v>
-      </c>
-      <c r="D145"/>
+        <v>0.0209719702074719</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00507121515079738</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0206974878099491</v>
+        <v>0.0194686182492963</v>
       </c>
       <c r="D146" t="n">
-        <v>0.00500659489502285</v>
+        <v>0.00593446863405789</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B147" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0192008986873014</v>
+        <v>0.019373927824829</v>
       </c>
       <c r="D147" t="n">
-        <v>0.00585458699555748</v>
+        <v>0.0130313917988485</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B148" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0190883150333064</v>
+        <v>0.0179563283043796</v>
       </c>
       <c r="D148" t="n">
-        <v>0.012838001249836</v>
+        <v>0.00998423644678831</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B149" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0177049970984185</v>
+        <v>0.0178561822256678</v>
       </c>
       <c r="D149" t="n">
-        <v>0.00984649802455643</v>
+        <v>0.00331717428316362</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0175983720703856</v>
+        <v>0.0176650311910475</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00326884646541883</v>
+        <v>0.00397646207922707</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0174683422471075</v>
+        <v>0.0172826710829321</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00433675754998142</v>
+        <v>0.00826073395968249</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B152" t="s">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="C152" t="n">
-        <v>0.017400018579225</v>
+        <v>0.017208207206382</v>
       </c>
       <c r="D152" t="n">
-        <v>0.0039132560543665</v>
+        <v>0.00607299719092432</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B153" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0170419853711769</v>
+        <v>0.0170667374487117</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00815725481652204</v>
+        <v>0.00464193813517276</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B154" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0168647735432856</v>
+        <v>0.016905824667936</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00593812803788504</v>
+        <v>0.00407949503596092</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B155" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0168188806644815</v>
+        <v>0.0166579986719353</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00457282023635471</v>
+        <v>0.0070830252519693</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B156" t="s">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0164230617466065</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0.00698184550013556</v>
-      </c>
+        <v>0.0165351013542464</v>
+      </c>
+      <c r="D156"/>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B157" t="s">
-        <v>272</v>
+        <v>149</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0162991624327317</v>
-      </c>
-      <c r="D157"/>
+        <v>0.0161551208400035</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.00425765674950489</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B158" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="C158" t="n">
-        <v>0.015939496331992</v>
+        <v>0.0152714499495797</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00419961909363021</v>
+        <v>0.0079175190987513</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B159" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0150511740605594</v>
+        <v>0.015248234399603</v>
       </c>
       <c r="D159" t="n">
-        <v>0.00780353305785579</v>
+        <v>0.00164806274414119</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B160" t="s">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="C160" t="n">
-        <v>0.01504702021073</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.00162631152524278</v>
-      </c>
+        <v>0.0145449193130603</v>
+      </c>
+      <c r="D160"/>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B161" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0146666135080839</v>
+        <v>0.0143620097986818</v>
       </c>
       <c r="D161" t="n">
-        <v>0.00109593504962922</v>
+        <v>0.00500606145536849</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B162" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0142318056962936</v>
-      </c>
-      <c r="D162"/>
+        <v>0.0142599484370969</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.00209716350582463</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B163" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0141565493962822</v>
+        <v>0.0140808114495895</v>
       </c>
       <c r="D163" t="n">
-        <v>0.00493869471385782</v>
+        <v>0.00169554432490574</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B164" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0140572294145009</v>
+        <v>0.0139812167401897</v>
       </c>
       <c r="D164" t="n">
-        <v>0.00206737573346722</v>
+        <v>0.0042312435563127</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B165" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0138756918533391</v>
+        <v>0.0134358834712381</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00167296056388729</v>
+        <v>0.000289288718725805</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B166" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0137995188416412</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.00417619415255558</v>
-      </c>
+        <v>0.0130490543697521</v>
+      </c>
+      <c r="D166"/>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B167" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0132393793539659</v>
+        <v>0.0127567705955461</v>
       </c>
       <c r="D167" t="n">
-        <v>0.00029825902958435</v>
+        <v>0.00116515154097036</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B168" t="s">
-        <v>124</v>
+        <v>273</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0128629832649481</v>
+        <v>0.0126696542442587</v>
       </c>
       <c r="D168"/>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B169" t="s">
-        <v>274</v>
+        <v>93</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0125071558943955</v>
-      </c>
-      <c r="D169"/>
+        <v>0.0125175053335992</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.00141592241424564</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B170" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0123475621192286</v>
+        <v>0.0123887751089786</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00139722014161033</v>
+        <v>0.00264726187910561</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B171" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0122271864158986</v>
+        <v>0.0123878464869796</v>
       </c>
       <c r="D171"/>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B172" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0122059874581489</v>
+        <v>0.011320511576803</v>
       </c>
       <c r="D172" t="n">
-        <v>0.00260724038862043</v>
+        <v>0.00356095368494913</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B173" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0111725669150917</v>
+        <v>0.011049005719826</v>
       </c>
       <c r="D173" t="n">
-        <v>0.00351436983576528</v>
+        <v>0.00310772515567478</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B174" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0109675959114444</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0.00306268415749463</v>
-      </c>
+        <v>0.0110259642864742</v>
+      </c>
+      <c r="D174"/>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B175" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0107886366019007</v>
-      </c>
-      <c r="D175"/>
+        <v>0.0106438653532959</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.000993378499693028</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B176" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0104897599448703</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0.00097935938327651</v>
-      </c>
+        <v>0.010355412144836</v>
+      </c>
+      <c r="D176"/>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B177" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0102211347734935</v>
-      </c>
-      <c r="D177"/>
+        <v>0.00977241164604731</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.00201376677313978</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B178" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="C178" t="n">
-        <v>0.00964329129137322</v>
+        <v>0.009673281247647</v>
       </c>
       <c r="D178" t="n">
-        <v>0.00198673018851637</v>
+        <v>0.00218896334597318</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B179" t="s">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="C179" t="n">
-        <v>0.00953305671107483</v>
+        <v>0.00924559277820211</v>
       </c>
       <c r="D179" t="n">
-        <v>0.0021571566526205</v>
+        <v>0.00338989481791672</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B180" t="s">
         <v>276</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00911741390297989</v>
-      </c>
-      <c r="D180" t="n">
-        <v>0.00334214614523539</v>
-      </c>
+        <v>0.00921187219186102</v>
+      </c>
+      <c r="D180"/>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>185</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00909249080400391</v>
+        <v>0.0088544107610955</v>
       </c>
       <c r="D181"/>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B182" t="s">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="C182" t="n">
-        <v>0.00872666554662074</v>
-      </c>
-      <c r="D182"/>
+        <v>0.00851212649612723</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.00356952894495301</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B183" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C183" t="n">
-        <v>0.00840223555132988</v>
+        <v>0.00844770334494201</v>
       </c>
       <c r="D183" t="n">
-        <v>0.00352324049277413</v>
+        <v>0.00392651183649352</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B184" t="s">
-        <v>106</v>
+        <v>277</v>
       </c>
       <c r="C184" t="n">
-        <v>0.00832844026056879</v>
+        <v>0.00787961883701331</v>
       </c>
       <c r="D184" t="n">
-        <v>0.00387134051863828</v>
+        <v>0.00130442577391692</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B185" t="s">
         <v>278</v>
       </c>
       <c r="C185" t="n">
-        <v>0.00777480369641945</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0.00128504185810732</v>
-      </c>
+        <v>0.00708793956337197</v>
+      </c>
+      <c r="D185"/>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B186" t="s">
         <v>279</v>
       </c>
       <c r="C186" t="n">
-        <v>0.00699284862785791</v>
+        <v>0.00695981874693831</v>
       </c>
       <c r="D186"/>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B187" t="s">
         <v>280</v>
       </c>
       <c r="C187" t="n">
-        <v>0.00685213338398429</v>
+        <v>0.00692456013041127</v>
       </c>
       <c r="D187"/>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B188" t="s">
-        <v>281</v>
+        <v>125</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00683059065935217</v>
-      </c>
-      <c r="D188"/>
+        <v>0.00684574333824053</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.00208612220260079</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B189" t="s">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00674699801244191</v>
+        <v>0.00683526732131357</v>
       </c>
       <c r="D189" t="n">
-        <v>0.00205567342838677</v>
+        <v>0.000262141265942254</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B190" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0067017640201625</v>
+        <v>0.00667159769397817</v>
       </c>
       <c r="D190" t="n">
-        <v>0.00025307949583696</v>
+        <v>0.000194466533363914</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B191" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00657396868162012</v>
+        <v>0.00653630907648922</v>
       </c>
       <c r="D191" t="n">
-        <v>0.000190007450251373</v>
+        <v>0.00171170930661684</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B192" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C192" t="n">
-        <v>0.00644794947197027</v>
-      </c>
-      <c r="D192" t="n">
-        <v>0.00168965306098622</v>
-      </c>
+        <v>0.00645145624132455</v>
+      </c>
+      <c r="D192"/>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B193" t="s">
-        <v>169</v>
+        <v>281</v>
       </c>
       <c r="C193" t="n">
-        <v>0.00635381464066557</v>
+        <v>0.00554877761935734</v>
       </c>
       <c r="D193"/>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B194" t="s">
         <v>282</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00547213852895987</v>
+        <v>0.00534085334987894</v>
       </c>
       <c r="D194"/>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B195" t="s">
         <v>283</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00527235267578914</v>
-      </c>
-      <c r="D195"/>
+        <v>0.00499758242403665</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.00127838625142545</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B196" t="s">
-        <v>284</v>
+        <v>60</v>
       </c>
       <c r="C196" t="n">
-        <v>0.00492778367063607</v>
+        <v>0.00486359968123389</v>
       </c>
       <c r="D196" t="n">
-        <v>0.00126108160336021</v>
+        <v>0.00105811985306826</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B197" t="s">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0047989570314464</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.00104440942654483</v>
-      </c>
+        <v>0.00485579345255424</v>
+      </c>
+      <c r="D197"/>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B198" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00479245410792048</v>
-      </c>
-      <c r="D198"/>
+        <v>0.00461983640647903</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.00184506880797268</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B199" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="C199" t="n">
-        <v>0.00455906504199248</v>
+        <v>0.00451916797789277</v>
       </c>
       <c r="D199" t="n">
-        <v>0.00182138480443802</v>
+        <v>0.00294227844459761</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B200" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00446103418602026</v>
+        <v>0.00443654963941336</v>
       </c>
       <c r="D200" t="n">
-        <v>0.00290466293325108</v>
+        <v>0.00116534405248105</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B201" t="s">
-        <v>116</v>
+        <v>218</v>
       </c>
       <c r="C201" t="n">
-        <v>0.00437512111265361</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.0011499611728173</v>
-      </c>
+        <v>0.00442560931148686</v>
+      </c>
+      <c r="D201"/>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B202" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00436145637907712</v>
-      </c>
-      <c r="D202"/>
+        <v>0.00436774455317005</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.00108252125013055</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B203" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C203" t="n">
-        <v>0.00430304465630466</v>
+        <v>0.00404368449493344</v>
       </c>
       <c r="D203" t="n">
-        <v>0.00106634991065256</v>
+        <v>0.00126921455560493</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B204" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C204" t="n">
-        <v>0.00404160994221862</v>
-      </c>
-      <c r="D204"/>
+        <v>0.00398111858774636</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.00100186071804999</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B205" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="C205" t="n">
-        <v>0.00398669318275084</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0.00124999174559935</v>
-      </c>
+        <v>0.00389597555820699</v>
+      </c>
+      <c r="D205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B206" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00392948464406688</v>
-      </c>
-      <c r="D206" t="n">
-        <v>0.000988605927725802</v>
-      </c>
+        <v>0.00381237055885357</v>
+      </c>
+      <c r="D206"/>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B207" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00384294133141578</v>
+        <v>0.00377835977813777</v>
       </c>
       <c r="D207"/>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B208" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00372385475389489</v>
-      </c>
-      <c r="D208"/>
+        <v>0.00350438726897579</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.0011757091952582</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B209" t="s">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00345494311011605</v>
-      </c>
-      <c r="D209" t="n">
-        <v>0.00115874913175866</v>
-      </c>
+        <v>0.00329602770793533</v>
+      </c>
+      <c r="D209"/>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B210" t="s">
-        <v>288</v>
+        <v>148</v>
       </c>
       <c r="C210" t="n">
-        <v>0.00325255035808691</v>
-      </c>
-      <c r="D210"/>
+        <v>0.00326541220140362</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.00174564339556838</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B211" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C211" t="n">
-        <v>0.00322161133866845</v>
-      </c>
-      <c r="D211" t="n">
-        <v>0.00172242361352604</v>
-      </c>
+        <v>0.0031156719040542</v>
+      </c>
+      <c r="D211"/>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B212" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00307324728166082</v>
-      </c>
-      <c r="D212"/>
+        <v>0.00311393073780596</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.000573125122682993</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B213" t="s">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00307264568961657</v>
+        <v>0.00297307038832261</v>
       </c>
       <c r="D213" t="n">
-        <v>0.000565691955411315</v>
+        <v>0.000737421526801622</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="C214" t="n">
-        <v>0.00292900842724232</v>
-      </c>
-      <c r="D214" t="n">
-        <v>0.000728956087926004</v>
-      </c>
+        <v>0.00294071371554265</v>
+      </c>
+      <c r="D214"/>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B215" t="s">
-        <v>289</v>
+        <v>170</v>
       </c>
       <c r="C215" t="n">
-        <v>0.00290299673313864</v>
-      </c>
-      <c r="D215"/>
+        <v>0.00294004626848082</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.00138350924121507</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B216" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="C216" t="n">
-        <v>0.00289852776366709</v>
-      </c>
-      <c r="D216" t="n">
-        <v>0.00136424539014174</v>
-      </c>
+        <v>0.00280992311086168</v>
+      </c>
+      <c r="D216"/>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00276918547415378</v>
-      </c>
-      <c r="D217"/>
+        <v>0.00259126164951908</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.000172263776544074</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B218" t="s">
-        <v>64</v>
+        <v>289</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00255478952847988</v>
+        <v>0.0025902459692076</v>
       </c>
       <c r="D218" t="n">
-        <v>0.000170339576080511</v>
+        <v>0.00155677877880343</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B219" t="s">
-        <v>290</v>
+        <v>157</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00255458899779847</v>
+        <v>0.00239651220465243</v>
       </c>
       <c r="D219" t="n">
-        <v>0.0015350900421055</v>
+        <v>0.00100762679337712</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B220" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0023643713228553</v>
+        <v>0.00236374925974788</v>
       </c>
       <c r="D220" t="n">
-        <v>0.000993710605493749</v>
+        <v>0.00139662141962802</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B221" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="C221" t="n">
-        <v>0.00233165617454429</v>
+        <v>0.00206870863898209</v>
       </c>
       <c r="D221" t="n">
-        <v>0.00137745273103341</v>
+        <v>0.00057207264784769</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B222" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="C222" t="n">
-        <v>0.00204151692577556</v>
+        <v>0.00206574865636007</v>
       </c>
       <c r="D222" t="n">
-        <v>0.000564269459936274</v>
+        <v>0.000725807296783265</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B223" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="C223" t="n">
-        <v>0.00203217792546962</v>
-      </c>
-      <c r="D223" t="n">
-        <v>0.000714249754356442</v>
-      </c>
+        <v>0.00193896273405007</v>
+      </c>
+      <c r="D223"/>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B224" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="C224" t="n">
-        <v>0.00191185951662002</v>
+        <v>0.00163333001860743</v>
       </c>
       <c r="D224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B225" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="C225" t="n">
-        <v>0.00163587200451122</v>
-      </c>
-      <c r="D225"/>
+        <v>0.00159601102201996</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.000578987834272048</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B226" t="s">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="C226" t="n">
-        <v>0.00161192291170211</v>
-      </c>
-      <c r="D226"/>
+        <v>0.00158335854728269</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.000213652584719328</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B227" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="C227" t="n">
-        <v>0.00157554091664521</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.000571561856747628</v>
-      </c>
+        <v>0.0015589822198072</v>
+      </c>
+      <c r="D227"/>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B228" t="s">
-        <v>291</v>
+        <v>163</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0015591260480093</v>
-      </c>
-      <c r="D228" t="n">
-        <v>0.000209109478565557</v>
-      </c>
+        <v>0.00154310858751066</v>
+      </c>
+      <c r="D228"/>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B229" t="s">
         <v>292</v>
       </c>
       <c r="C229" t="n">
-        <v>0.00153964592467175</v>
-      </c>
-      <c r="D229"/>
+        <v>0.00149867982874284</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.000219726457661791</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B230" t="s">
-        <v>293</v>
+        <v>188</v>
       </c>
       <c r="C230" t="n">
-        <v>0.00153311435390563</v>
+        <v>0.00146060632678113</v>
       </c>
       <c r="D230"/>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B231" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C231" t="n">
-        <v>0.00147481722009398</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.000217029831768999</v>
-      </c>
+        <v>0.00145233578710195</v>
+      </c>
+      <c r="D231"/>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B232" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="C232" t="n">
-        <v>0.00144055512081205</v>
+        <v>0.00144136643973798</v>
       </c>
       <c r="D232"/>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B233" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="C233" t="n">
-        <v>0.00142130417539611</v>
-      </c>
-      <c r="D233"/>
+        <v>0.00143173198649767</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.000772387335902827</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B234" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="C234" t="n">
-        <v>0.00140792591422165</v>
-      </c>
-      <c r="D234" t="n">
-        <v>0.000759604411191498</v>
-      </c>
+        <v>0.00133472000703273</v>
+      </c>
+      <c r="D234"/>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B235" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C235" t="n">
-        <v>0.00131536668112807</v>
-      </c>
-      <c r="D235"/>
+        <v>0.00124484680918561</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.000598584282447899</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B236" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C236" t="n">
-        <v>0.00122870877951616</v>
+        <v>0.00123802724137997</v>
       </c>
       <c r="D236" t="n">
-        <v>0.00059102850490238</v>
+        <v>0.000515417366786408</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B237" t="s">
-        <v>200</v>
+        <v>294</v>
       </c>
       <c r="C237" t="n">
-        <v>0.00121948436817102</v>
-      </c>
-      <c r="D237" t="n">
-        <v>0.000508381341040375</v>
-      </c>
+        <v>0.00121501482746561</v>
+      </c>
+      <c r="D237"/>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B238" t="s">
         <v>295</v>
       </c>
       <c r="C238" t="n">
-        <v>0.00119882970798518</v>
+        <v>0.00118094600787487</v>
       </c>
       <c r="D238"/>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B239" t="s">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="C239" t="n">
-        <v>0.00116579944003194</v>
-      </c>
-      <c r="D239"/>
+        <v>0.00111806088687561</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.000277099933158837</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B240" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C240" t="n">
-        <v>0.00112964662289666</v>
+        <v>0.0011167840316269</v>
       </c>
       <c r="D240" t="n">
-        <v>0.000254443878742804</v>
+        <v>0.000283173806101299</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B241" t="s">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="C241" t="n">
-        <v>0.00110082749925316</v>
-      </c>
-      <c r="D241" t="n">
-        <v>0.000278873408060838</v>
-      </c>
+        <v>0.000966405306653128</v>
+      </c>
+      <c r="D241"/>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B242" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="C242" t="n">
-        <v>0.000952606678446548</v>
-      </c>
-      <c r="D242"/>
+        <v>0.000963996693343051</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.000156710025883741</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B243" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C243" t="n">
-        <v>0.000950057074068544</v>
+        <v>0.000947136400172506</v>
       </c>
       <c r="D243" t="n">
-        <v>0.000155571131975538</v>
+        <v>0.000224363941732725</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B244" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
       <c r="C244" t="n">
-        <v>0.00093395732507486</v>
-      </c>
-      <c r="D244" t="n">
-        <v>0.000220757056805913</v>
-      </c>
+        <v>0.000913212677769122</v>
+      </c>
+      <c r="D244"/>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B245" t="s">
         <v>298</v>
       </c>
       <c r="C245" t="n">
-        <v>0.000899981698194952</v>
-      </c>
-      <c r="D245"/>
+        <v>0.000904187632715698</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.000227154640111694</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B246" t="s">
-        <v>299</v>
+        <v>198</v>
       </c>
       <c r="C246" t="n">
-        <v>0.000891215642693053</v>
+        <v>0.000851517353706166</v>
       </c>
       <c r="D246" t="n">
-        <v>0.000223268882374268</v>
+        <v>0.000222250398107476</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B247" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="C247" t="n">
-        <v>0.000840366791333999</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.000219561913995164</v>
-      </c>
+        <v>0.000848528351646672</v>
+      </c>
+      <c r="D247"/>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B248" t="s">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="C248" t="n">
-        <v>0.00083423628193071</v>
+        <v>0.000835034313222743</v>
       </c>
       <c r="D248"/>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B249" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C249" t="n">
-        <v>0.00082306385825182</v>
-      </c>
-      <c r="D249"/>
+        <v>0.000822613993985233</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.0000183242180324971</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B250" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C250" t="n">
-        <v>0.000809972069479376</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.0000171371325066804</v>
-      </c>
+        <v>0.000816606970428774</v>
+      </c>
+      <c r="D250"/>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B251" t="s">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="C251" t="n">
-        <v>0.000803068084590626</v>
+        <v>0.000742375249378426</v>
       </c>
       <c r="D251"/>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B252" t="s">
         <v>301</v>
       </c>
       <c r="C252" t="n">
-        <v>0.000730046269315004</v>
-      </c>
-      <c r="D252"/>
+        <v>0.000735004312260838</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.00015972644251395</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B253" t="s">
-        <v>302</v>
+        <v>193</v>
       </c>
       <c r="C253" t="n">
-        <v>0.000724030348872524</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.000158042444228274</v>
-      </c>
+        <v>0.000725602014520294</v>
+      </c>
+      <c r="D253"/>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B254" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="C254" t="n">
-        <v>0.000716009121615885</v>
+        <v>0.000649629127221696</v>
       </c>
       <c r="D254"/>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B255" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="C255" t="n">
-        <v>0.000640953352285901</v>
+        <v>0.000640604082168272</v>
       </c>
       <c r="D255"/>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C256" t="n">
-        <v>0.000631700293700563</v>
-      </c>
-      <c r="D256"/>
+        <v>0.000634451961424459</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.000208625223668979</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="C257" t="n">
-        <v>0.000625197370174644</v>
-      </c>
-      <c r="D257" t="n">
-        <v>0.000206131749867588</v>
-      </c>
+        <v>0.000574875056296873</v>
+      </c>
+      <c r="D257"/>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B258" t="s">
         <v>303</v>
       </c>
       <c r="C258" t="n">
-        <v>0.000566098113637333</v>
-      </c>
-      <c r="D258"/>
+        <v>0.000527863567594151</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.000133255847595785</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B259" t="s">
         <v>304</v>
       </c>
       <c r="C259" t="n">
-        <v>0.000520061998632263</v>
-      </c>
-      <c r="D259" t="n">
-        <v>0.000131789815707402</v>
-      </c>
+        <v>0.000509117010988003</v>
+      </c>
+      <c r="D259"/>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B260" t="s">
         <v>305</v>
       </c>
       <c r="C260" t="n">
-        <v>0.000500524580814305</v>
-      </c>
-      <c r="D260"/>
+        <v>0.000472204286525125</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.000146101268075453</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B261" t="s">
         <v>306</v>
       </c>
       <c r="C261" t="n">
-        <v>0.000464629588840843</v>
-      </c>
-      <c r="D261" t="n">
-        <v>0.000143356367316521</v>
-      </c>
+        <v>0.000447682861862285</v>
+      </c>
+      <c r="D261"/>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B262" t="s">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="C262" t="n">
-        <v>0.000441539913237802</v>
+        <v>0.000424264175823336</v>
       </c>
       <c r="D262"/>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B263" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="C263" t="n">
-        <v>0.000417103817345254</v>
+        <v>0.000398349818161897</v>
       </c>
       <c r="D263"/>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B264" t="s">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="C264" t="n">
-        <v>0.000392868252134122</v>
+        <v>0.000398349818161897</v>
       </c>
       <c r="D264"/>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B265" t="s">
-        <v>308</v>
+        <v>162</v>
       </c>
       <c r="C265" t="n">
-        <v>0.000392868252134122</v>
+        <v>0.000293270435080071</v>
       </c>
       <c r="D265"/>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B266" t="s">
-        <v>162</v>
+        <v>308</v>
       </c>
       <c r="C266" t="n">
-        <v>0.000289509009484281</v>
+        <v>0.000268603913229877</v>
       </c>
       <c r="D266"/>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B267" t="s">
         <v>309</v>
       </c>
       <c r="C267" t="n">
-        <v>0.000264929677390722</v>
+        <v>0.000254558505494002</v>
       </c>
       <c r="D267"/>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B268" t="s">
         <v>310</v>
       </c>
       <c r="C268" t="n">
-        <v>0.000250262290407152</v>
+        <v>0.000236189201574975</v>
       </c>
       <c r="D268"/>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B269" t="s">
         <v>311</v>
       </c>
       <c r="C269" t="n">
-        <v>0.000233159888006389</v>
+        <v>0.000236189201574975</v>
       </c>
       <c r="D269"/>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B270" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="C270" t="n">
-        <v>0.000233159888006389</v>
+        <v>0.000199160399362213</v>
       </c>
       <c r="D270"/>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B271" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000196434126067061</v>
+        <v>0.000199160399362213</v>
       </c>
       <c r="D271"/>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B272" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C272" t="n">
-        <v>0.000196434126067061</v>
+        <v>0.000169705670329334</v>
       </c>
       <c r="D272"/>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B273" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="C273" t="n">
-        <v>0.000166841526938102</v>
+        <v>0.000132792945866456</v>
       </c>
       <c r="D273"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="s">
-        <v>256</v>
-      </c>
-      <c r="B274" t="s">
-        <v>159</v>
-      </c>
-      <c r="C274" t="n">
-        <v>0.00013094653496464</v>
-      </c>
-      <c r="D274"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
